--- a/pagina/data/informe_hombres.xlsx
+++ b/pagina/data/informe_hombres.xlsx
@@ -16,7 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detalle_departamento" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Categorias'!$A$1:$D$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Categorias'!$A$1:$D$59</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Indicadores_si'!$A$1:$D$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Historico_anual'!$A$1:$B$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Ubicaciones'!$A$1:$D$52</definedName>
@@ -42,6 +42,9 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
@@ -52,9 +55,6 @@
     <font>
       <i val="1"/>
       <color rgb="00595959"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <i val="1"/>
@@ -75,13 +75,19 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
     <border>
       <left style="thin">
@@ -103,21 +109,21 @@
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -500,7 +506,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Centro Emergencia Mujer y Familia · Enero - Julio 2026 (preliminar)</t>
+          <t>Centro Emergencia Mujer y Familia · Enero - Agosto 2026 (preliminar)</t>
         </is>
       </c>
     </row>
@@ -511,7 +517,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>17701</v>
+        <v>20286</v>
       </c>
     </row>
     <row r="6">
@@ -522,7 +528,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>2026-08-18 10:33</t>
+          <t>2026-09-18 09:54</t>
         </is>
       </c>
     </row>
@@ -541,7 +547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D58"/>
+  <dimension ref="A1:D59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -584,7 +590,7 @@
         </is>
       </c>
       <c r="C2" s="8" t="n">
-        <v>12477</v>
+        <v>14302</v>
       </c>
       <c r="D2" s="9" t="n">
         <v>70.5</v>
@@ -602,7 +608,7 @@
         </is>
       </c>
       <c r="C3" s="8" t="n">
-        <v>2975</v>
+        <v>3404</v>
       </c>
       <c r="D3" s="9" t="n">
         <v>16.8</v>
@@ -620,7 +626,7 @@
         </is>
       </c>
       <c r="C4" s="8" t="n">
-        <v>2249</v>
+        <v>2580</v>
       </c>
       <c r="D4" s="9" t="n">
         <v>12.7</v>
@@ -638,10 +644,10 @@
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>15705</v>
+        <v>17969</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>88.7</v>
+        <v>88.59999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -656,10 +662,10 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>1486</v>
+        <v>1726</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="7">
@@ -674,7 +680,7 @@
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>351</v>
+        <v>411</v>
       </c>
       <c r="D7" s="9" t="n">
         <v>2</v>
@@ -692,7 +698,7 @@
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="D8" s="9" t="n">
         <v>0.9</v>
@@ -710,7 +716,7 @@
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>8858</v>
+        <v>10133</v>
       </c>
       <c r="D9" s="9" t="n">
         <v>50</v>
@@ -728,10 +734,10 @@
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>4935</v>
+        <v>5624</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>27.9</v>
+        <v>27.7</v>
       </c>
     </row>
     <row r="11">
@@ -746,10 +752,10 @@
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>3908</v>
+        <v>4529</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>22.1</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="12">
@@ -764,10 +770,10 @@
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>15253</v>
+        <v>17439</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>86.2</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13">
@@ -782,10 +788,10 @@
         </is>
       </c>
       <c r="C13" s="8" t="n">
-        <v>1717</v>
+        <v>1956</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="14">
@@ -800,10 +806,10 @@
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>731</v>
+        <v>891</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="15">
@@ -818,10 +824,10 @@
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>10066</v>
+        <v>11490</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>56.9</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="16">
@@ -836,7 +842,7 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>6306</v>
+        <v>7225</v>
       </c>
       <c r="D16" s="9" t="n">
         <v>35.6</v>
@@ -854,10 +860,10 @@
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>1205</v>
+        <v>1439</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="18">
@@ -872,7 +878,7 @@
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="D18" s="9" t="n">
         <v>0.7</v>
@@ -890,10 +896,10 @@
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>11511</v>
+        <v>13251</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>65</v>
+        <v>65.3</v>
       </c>
     </row>
     <row r="20">
@@ -908,10 +914,10 @@
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>6190</v>
+        <v>7035</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>35</v>
+        <v>34.7</v>
       </c>
     </row>
     <row r="21">
@@ -926,10 +932,10 @@
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>15703</v>
+        <v>17941</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>88.7</v>
+        <v>88.40000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -944,7 +950,7 @@
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>950</v>
+        <v>1101</v>
       </c>
       <c r="D22" s="9" t="n">
         <v>5.4</v>
@@ -962,10 +968,10 @@
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>814</v>
+        <v>965</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="24">
@@ -980,10 +986,10 @@
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>234</v>
+        <v>279</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="25">
@@ -998,7 +1004,7 @@
         </is>
       </c>
       <c r="C25" s="8" t="n">
-        <v>314</v>
+        <v>362</v>
       </c>
       <c r="D25" s="9" t="n">
         <v>1.8</v>
@@ -1016,10 +1022,10 @@
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>2393</v>
+        <v>2711</v>
       </c>
       <c r="D26" s="9" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="27">
@@ -1034,10 +1040,10 @@
         </is>
       </c>
       <c r="C27" s="8" t="n">
-        <v>9761</v>
+        <v>11161</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>55.1</v>
+        <v>55</v>
       </c>
     </row>
     <row r="28">
@@ -1052,10 +1058,10 @@
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>4043</v>
+        <v>4613</v>
       </c>
       <c r="D28" s="9" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
     </row>
     <row r="29">
@@ -1088,7 +1094,7 @@
         </is>
       </c>
       <c r="C30" s="8" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D30" s="9" t="n">
         <v>0.1</v>
@@ -1106,7 +1112,7 @@
         </is>
       </c>
       <c r="C31" s="8" t="n">
-        <v>3723</v>
+        <v>4270</v>
       </c>
       <c r="D31" s="9" t="n">
         <v>21</v>
@@ -1124,7 +1130,7 @@
         </is>
       </c>
       <c r="C32" s="8" t="n">
-        <v>6841</v>
+        <v>7828</v>
       </c>
       <c r="D32" s="9" t="n">
         <v>38.6</v>
@@ -1142,10 +1148,10 @@
         </is>
       </c>
       <c r="C33" s="8" t="n">
-        <v>5287</v>
+        <v>6047</v>
       </c>
       <c r="D33" s="9" t="n">
-        <v>29.9</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="34">
@@ -1160,10 +1166,10 @@
         </is>
       </c>
       <c r="C34" s="8" t="n">
-        <v>1822</v>
+        <v>2105</v>
       </c>
       <c r="D34" s="9" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="35">
@@ -1178,7 +1184,7 @@
         </is>
       </c>
       <c r="C35" s="8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D35" s="9" t="n">
         <v>0</v>
@@ -1196,7 +1202,7 @@
         </is>
       </c>
       <c r="C36" s="8" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D36" s="9" t="n">
         <v>0.1</v>
@@ -1214,10 +1220,10 @@
         </is>
       </c>
       <c r="C37" s="8" t="n">
-        <v>7813</v>
+        <v>8978</v>
       </c>
       <c r="D37" s="9" t="n">
-        <v>44.1</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="38">
@@ -1232,10 +1238,10 @@
         </is>
       </c>
       <c r="C38" s="8" t="n">
-        <v>668</v>
+        <v>751</v>
       </c>
       <c r="D38" s="9" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="39">
@@ -1250,7 +1256,7 @@
         </is>
       </c>
       <c r="C39" s="8" t="n">
-        <v>207</v>
+        <v>247</v>
       </c>
       <c r="D39" s="9" t="n">
         <v>1.2</v>
@@ -1268,7 +1274,7 @@
         </is>
       </c>
       <c r="C40" s="8" t="n">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="D40" s="9" t="n">
         <v>0.6</v>
@@ -1286,7 +1292,7 @@
         </is>
       </c>
       <c r="C41" s="8" t="n">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="D41" s="9" t="n">
         <v>0.5</v>
@@ -1304,7 +1310,7 @@
         </is>
       </c>
       <c r="C42" s="8" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D42" s="9" t="n">
         <v>0.2</v>
@@ -1322,7 +1328,7 @@
         </is>
       </c>
       <c r="C43" s="8" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D43" s="9" t="n">
         <v>0.1</v>
@@ -1349,19 +1355,19 @@
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>lugar_ocurrencia</t>
+          <t>etnia</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>Casa de la persona usuaria</t>
+          <t>Perteneciente o parte de otro pueblo indígena u originario</t>
         </is>
       </c>
       <c r="C45" s="8" t="n">
-        <v>6362</v>
+        <v>1</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v>35.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1372,14 +1378,14 @@
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>Casa de ambos</t>
+          <t>Casa de la persona usuaria</t>
         </is>
       </c>
       <c r="C46" s="8" t="n">
-        <v>3508</v>
+        <v>7290</v>
       </c>
       <c r="D46" s="9" t="n">
-        <v>19.8</v>
+        <v>35.9</v>
       </c>
     </row>
     <row r="47">
@@ -1390,14 +1396,14 @@
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>Casa de la presunta persona agresora</t>
+          <t>Casa de ambos</t>
         </is>
       </c>
       <c r="C47" s="8" t="n">
-        <v>3156</v>
+        <v>4005</v>
       </c>
       <c r="D47" s="9" t="n">
-        <v>17.8</v>
+        <v>19.7</v>
       </c>
     </row>
     <row r="48">
@@ -1408,14 +1414,14 @@
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>Calle – vía pública</t>
+          <t>Casa de la presunta persona agresora</t>
         </is>
       </c>
       <c r="C48" s="8" t="n">
-        <v>1524</v>
+        <v>3594</v>
       </c>
       <c r="D48" s="9" t="n">
-        <v>8.6</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="49">
@@ -1426,14 +1432,14 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>Casa de un familiar de la persona usuaria</t>
+          <t>Calle – vía pública</t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
-        <v>1466</v>
+        <v>1783</v>
       </c>
       <c r="D49" s="9" t="n">
-        <v>8.300000000000001</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="50">
@@ -1444,14 +1450,14 @@
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>Otro lugar</t>
+          <t>Casa de un familiar de la persona usuaria</t>
         </is>
       </c>
       <c r="C50" s="8" t="n">
-        <v>1096</v>
+        <v>1677</v>
       </c>
       <c r="D50" s="9" t="n">
-        <v>6.2</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="51">
@@ -1462,14 +1468,14 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>Centro de estudios de la persona usuaria</t>
+          <t>Otro lugar</t>
         </is>
       </c>
       <c r="C51" s="8" t="n">
-        <v>231</v>
+        <v>1249</v>
       </c>
       <c r="D51" s="9" t="n">
-        <v>1.3</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="52">
@@ -1480,14 +1486,14 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>Centro de labores de la persona usuaria</t>
+          <t>Centro de estudios de la persona usuaria</t>
         </is>
       </c>
       <c r="C52" s="8" t="n">
-        <v>146</v>
+        <v>276</v>
       </c>
       <c r="D52" s="9" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="53">
@@ -1498,14 +1504,14 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>Lugar desolado</t>
+          <t>Centro de labores de la persona usuaria</t>
         </is>
       </c>
       <c r="C53" s="8" t="n">
-        <v>84</v>
+        <v>169</v>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="54">
@@ -1516,11 +1522,11 @@
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>Centro poblado</t>
+          <t>Lugar desolado</t>
         </is>
       </c>
       <c r="C54" s="8" t="n">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="D54" s="9" t="n">
         <v>0.5</v>
@@ -1534,32 +1540,32 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>Hotel / Hostal</t>
+          <t>Centro poblado</t>
         </is>
       </c>
       <c r="C55" s="8" t="n">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>ambito_violencia</t>
+          <t>lugar_ocurrencia</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>En el ámbito privado</t>
+          <t>Hotel / Hostal</t>
         </is>
       </c>
       <c r="C56" s="8" t="n">
-        <v>15241</v>
+        <v>55</v>
       </c>
       <c r="D56" s="9" t="n">
-        <v>86.09999999999999</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="57">
@@ -1570,14 +1576,14 @@
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>En el ámbito público</t>
+          <t>En el ámbito privado</t>
         </is>
       </c>
       <c r="C57" s="8" t="n">
-        <v>2459</v>
+        <v>17448</v>
       </c>
       <c r="D57" s="9" t="n">
-        <v>13.9</v>
+        <v>86</v>
       </c>
     </row>
     <row r="58">
@@ -1588,18 +1594,36 @@
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
+          <t>En el ámbito público</t>
+        </is>
+      </c>
+      <c r="C58" s="8" t="n">
+        <v>2837</v>
+      </c>
+      <c r="D58" s="9" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>ambito_violencia</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
           <t>En el ámbito estatal</t>
         </is>
       </c>
-      <c r="C58" s="8" t="n">
+      <c r="C59" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="D58" s="9" t="n">
+      <c r="D59" s="9" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D58"/>
+  <autoFilter ref="A1:D59"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1653,7 +1677,7 @@
         </is>
       </c>
       <c r="C2" s="8" t="n">
-        <v>1219</v>
+        <v>1408</v>
       </c>
       <c r="D2" s="9" t="n">
         <v>6.9</v>
@@ -1671,7 +1695,7 @@
         </is>
       </c>
       <c r="C3" s="8" t="n">
-        <v>209</v>
+        <v>241</v>
       </c>
       <c r="D3" s="9" t="n">
         <v>1.2</v>
@@ -1689,10 +1713,10 @@
         </is>
       </c>
       <c r="C4" s="8" t="n">
-        <v>3249</v>
+        <v>3700</v>
       </c>
       <c r="D4" s="9" t="n">
-        <v>18.4</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="5">
@@ -1707,10 +1731,10 @@
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>11608</v>
+        <v>13229</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>65.59999999999999</v>
+        <v>65.2</v>
       </c>
     </row>
     <row r="6">
@@ -1725,10 +1749,10 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="7">
@@ -1743,7 +1767,7 @@
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D7" s="9" t="n">
         <v>0</v>
@@ -1779,7 +1803,7 @@
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D9" s="9" t="n">
         <v>0</v>
@@ -1797,10 +1821,10 @@
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>411</v>
+        <v>498</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="11">
@@ -1815,10 +1839,10 @@
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>492</v>
+        <v>554</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="12">
@@ -1833,10 +1857,10 @@
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>188</v>
+        <v>212</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1851,7 +1875,7 @@
         </is>
       </c>
       <c r="C13" s="8" t="n">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="D13" s="9" t="n">
         <v>0.7</v>
@@ -1869,7 +1893,7 @@
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="D14" s="9" t="n">
         <v>0.9</v>
@@ -1887,10 +1911,10 @@
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>286</v>
+        <v>338</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="16">
@@ -1905,10 +1929,10 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>12898</v>
+        <v>14821</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>72.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -1923,10 +1947,10 @@
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>3746</v>
+        <v>4268</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>21.2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18">
@@ -1941,7 +1965,7 @@
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>272</v>
+        <v>306</v>
       </c>
       <c r="D18" s="9" t="n">
         <v>1.5</v>
@@ -1959,7 +1983,7 @@
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>254</v>
+        <v>293</v>
       </c>
       <c r="D19" s="9" t="n">
         <v>1.4</v>
@@ -1977,10 +2001,10 @@
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>525</v>
+        <v>594</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="21">
@@ -1995,10 +2019,10 @@
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>14214</v>
+        <v>16302</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>80.3</v>
+        <v>80.40000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -2013,10 +2037,10 @@
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>2303</v>
+        <v>2659</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="23">
@@ -2031,7 +2055,7 @@
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>295</v>
+        <v>348</v>
       </c>
       <c r="D23" s="9" t="n">
         <v>1.7</v>
@@ -2049,10 +2073,10 @@
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>6640</v>
+        <v>7566</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>37.5</v>
+        <v>37.3</v>
       </c>
     </row>
     <row r="25">
@@ -2067,10 +2091,10 @@
         </is>
       </c>
       <c r="C25" s="8" t="n">
-        <v>13830</v>
+        <v>15854</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>78.09999999999999</v>
+        <v>78.2</v>
       </c>
     </row>
     <row r="26">
@@ -2085,7 +2109,7 @@
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="D26" s="9" t="n">
         <v>0.5</v>
@@ -2167,7 +2191,7 @@
         <v>2026</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>17701</v>
+        <v>20286</v>
       </c>
     </row>
   </sheetData>
@@ -2225,10 +2249,10 @@
         </is>
       </c>
       <c r="C2" s="8" t="n">
-        <v>5160</v>
+        <v>5946</v>
       </c>
       <c r="D2" s="9" t="n">
-        <v>29.2</v>
+        <v>29.3</v>
       </c>
     </row>
     <row r="3">
@@ -2243,7 +2267,7 @@
         </is>
       </c>
       <c r="C3" s="8" t="n">
-        <v>2086</v>
+        <v>2384</v>
       </c>
       <c r="D3" s="9" t="n">
         <v>11.8</v>
@@ -2261,10 +2285,10 @@
         </is>
       </c>
       <c r="C4" s="8" t="n">
-        <v>1134</v>
+        <v>1275</v>
       </c>
       <c r="D4" s="9" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="5">
@@ -2279,10 +2303,10 @@
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>962</v>
+        <v>1136</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="6">
@@ -2297,10 +2321,10 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>857</v>
+        <v>987</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="7">
@@ -2315,7 +2339,7 @@
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>733</v>
+        <v>825</v>
       </c>
       <c r="D7" s="9" t="n">
         <v>4.1</v>
@@ -2333,7 +2357,7 @@
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>674</v>
+        <v>765</v>
       </c>
       <c r="D8" s="9" t="n">
         <v>3.8</v>
@@ -2351,7 +2375,7 @@
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>644</v>
+        <v>722</v>
       </c>
       <c r="D9" s="9" t="n">
         <v>3.6</v>
@@ -2369,7 +2393,7 @@
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>615</v>
+        <v>715</v>
       </c>
       <c r="D10" s="9" t="n">
         <v>3.5</v>
@@ -2387,10 +2411,10 @@
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>563</v>
+        <v>630</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="12">
@@ -2401,11 +2425,11 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>HUANUCO</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>510</v>
+        <v>580</v>
       </c>
       <c r="D12" s="9" t="n">
         <v>2.9</v>
@@ -2419,11 +2443,11 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>HUANUCO</t>
+          <t>AYACUCHO</t>
         </is>
       </c>
       <c r="C13" s="8" t="n">
-        <v>498</v>
+        <v>574</v>
       </c>
       <c r="D13" s="9" t="n">
         <v>2.8</v>
@@ -2441,10 +2465,10 @@
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>455</v>
+        <v>509</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="15">
@@ -2459,7 +2483,7 @@
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>360</v>
+        <v>415</v>
       </c>
       <c r="D15" s="9" t="n">
         <v>2</v>
@@ -2473,14 +2497,14 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>HUANCAVELICA</t>
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>298</v>
+        <v>332</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="17">
@@ -2491,11 +2515,11 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>HUANCAVELICA</t>
+          <t>TACNA</t>
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>283</v>
+        <v>331</v>
       </c>
       <c r="D17" s="9" t="n">
         <v>1.6</v>
@@ -2513,10 +2537,10 @@
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>259</v>
+        <v>316</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="19">
@@ -2531,10 +2555,10 @@
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>252</v>
+        <v>315</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="20">
@@ -2549,7 +2573,7 @@
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>246</v>
+        <v>286</v>
       </c>
       <c r="D20" s="9" t="n">
         <v>1.4</v>
@@ -2567,7 +2591,7 @@
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>221</v>
+        <v>241</v>
       </c>
       <c r="D21" s="9" t="n">
         <v>1.2</v>
@@ -2581,11 +2605,11 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>MOQUEGUA</t>
+          <t>UCAYALI</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>207</v>
+        <v>234</v>
       </c>
       <c r="D22" s="9" t="n">
         <v>1.2</v>
@@ -2599,14 +2623,14 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>UCAYALI</t>
+          <t>MOQUEGUA</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>206</v>
+        <v>228</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="24">
@@ -2621,7 +2645,7 @@
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="D24" s="9" t="n">
         <v>1</v>
@@ -2639,7 +2663,7 @@
         </is>
       </c>
       <c r="C25" s="8" t="n">
-        <v>168</v>
+        <v>190</v>
       </c>
       <c r="D25" s="9" t="n">
         <v>0.9</v>
@@ -2657,10 +2681,10 @@
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="27">
@@ -2675,10 +2699,10 @@
         </is>
       </c>
       <c r="C27" s="8" t="n">
-        <v>4345</v>
+        <v>5044</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>24.5</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="28">
@@ -2693,7 +2717,7 @@
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>2086</v>
+        <v>2384</v>
       </c>
       <c r="D28" s="9" t="n">
         <v>11.8</v>
@@ -2711,10 +2735,10 @@
         </is>
       </c>
       <c r="C29" s="8" t="n">
-        <v>1134</v>
+        <v>1275</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="30">
@@ -2729,10 +2753,10 @@
         </is>
       </c>
       <c r="C30" s="8" t="n">
-        <v>962</v>
+        <v>1136</v>
       </c>
       <c r="D30" s="9" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="31">
@@ -2747,10 +2771,10 @@
         </is>
       </c>
       <c r="C31" s="8" t="n">
-        <v>857</v>
+        <v>987</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="32">
@@ -2765,10 +2789,10 @@
         </is>
       </c>
       <c r="C32" s="8" t="n">
-        <v>815</v>
+        <v>902</v>
       </c>
       <c r="D32" s="9" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="33">
@@ -2783,7 +2807,7 @@
         </is>
       </c>
       <c r="C33" s="8" t="n">
-        <v>733</v>
+        <v>825</v>
       </c>
       <c r="D33" s="9" t="n">
         <v>4.1</v>
@@ -2801,7 +2825,7 @@
         </is>
       </c>
       <c r="C34" s="8" t="n">
-        <v>674</v>
+        <v>765</v>
       </c>
       <c r="D34" s="9" t="n">
         <v>3.8</v>
@@ -2819,7 +2843,7 @@
         </is>
       </c>
       <c r="C35" s="8" t="n">
-        <v>644</v>
+        <v>722</v>
       </c>
       <c r="D35" s="9" t="n">
         <v>3.6</v>
@@ -2837,7 +2861,7 @@
         </is>
       </c>
       <c r="C36" s="8" t="n">
-        <v>615</v>
+        <v>715</v>
       </c>
       <c r="D36" s="9" t="n">
         <v>3.5</v>
@@ -2855,10 +2879,10 @@
         </is>
       </c>
       <c r="C37" s="8" t="n">
-        <v>563</v>
+        <v>630</v>
       </c>
       <c r="D37" s="9" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="38">
@@ -2869,11 +2893,11 @@
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>HUANUCO</t>
         </is>
       </c>
       <c r="C38" s="8" t="n">
-        <v>510</v>
+        <v>580</v>
       </c>
       <c r="D38" s="9" t="n">
         <v>2.9</v>
@@ -2887,11 +2911,11 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>HUANUCO</t>
+          <t>AYACUCHO</t>
         </is>
       </c>
       <c r="C39" s="8" t="n">
-        <v>498</v>
+        <v>574</v>
       </c>
       <c r="D39" s="9" t="n">
         <v>2.8</v>
@@ -2909,10 +2933,10 @@
         </is>
       </c>
       <c r="C40" s="8" t="n">
-        <v>455</v>
+        <v>509</v>
       </c>
       <c r="D40" s="9" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="41">
@@ -2927,7 +2951,7 @@
         </is>
       </c>
       <c r="C41" s="8" t="n">
-        <v>360</v>
+        <v>415</v>
       </c>
       <c r="D41" s="9" t="n">
         <v>2</v>
@@ -2941,14 +2965,14 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>HUANCAVELICA</t>
         </is>
       </c>
       <c r="C42" s="8" t="n">
-        <v>298</v>
+        <v>332</v>
       </c>
       <c r="D42" s="9" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="43">
@@ -2959,11 +2983,11 @@
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>HUANCAVELICA</t>
+          <t>TACNA</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
-        <v>283</v>
+        <v>331</v>
       </c>
       <c r="D43" s="9" t="n">
         <v>1.6</v>
@@ -2981,10 +3005,10 @@
         </is>
       </c>
       <c r="C44" s="8" t="n">
-        <v>259</v>
+        <v>316</v>
       </c>
       <c r="D44" s="9" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="45">
@@ -2999,10 +3023,10 @@
         </is>
       </c>
       <c r="C45" s="8" t="n">
-        <v>252</v>
+        <v>315</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="46">
@@ -3017,7 +3041,7 @@
         </is>
       </c>
       <c r="C46" s="8" t="n">
-        <v>246</v>
+        <v>286</v>
       </c>
       <c r="D46" s="9" t="n">
         <v>1.4</v>
@@ -3035,7 +3059,7 @@
         </is>
       </c>
       <c r="C47" s="8" t="n">
-        <v>221</v>
+        <v>241</v>
       </c>
       <c r="D47" s="9" t="n">
         <v>1.2</v>
@@ -3049,11 +3073,11 @@
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>MOQUEGUA</t>
+          <t>UCAYALI</t>
         </is>
       </c>
       <c r="C48" s="8" t="n">
-        <v>207</v>
+        <v>234</v>
       </c>
       <c r="D48" s="9" t="n">
         <v>1.2</v>
@@ -3067,14 +3091,14 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>UCAYALI</t>
+          <t>MOQUEGUA</t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
-        <v>206</v>
+        <v>228</v>
       </c>
       <c r="D49" s="9" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="50">
@@ -3089,7 +3113,7 @@
         </is>
       </c>
       <c r="C50" s="8" t="n">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="D50" s="9" t="n">
         <v>1</v>
@@ -3107,7 +3131,7 @@
         </is>
       </c>
       <c r="C51" s="8" t="n">
-        <v>168</v>
+        <v>190</v>
       </c>
       <c r="D51" s="9" t="n">
         <v>0.9</v>
@@ -3125,10 +3149,10 @@
         </is>
       </c>
       <c r="C52" s="8" t="n">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="D52" s="9" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
     </row>
   </sheetData>
@@ -3202,7 +3226,7 @@
         </is>
       </c>
       <c r="E2" s="8" t="n">
-        <v>12493</v>
+        <v>14313</v>
       </c>
       <c r="F2" s="9" t="n">
         <v>70.59999999999999</v>
@@ -3224,10 +3248,10 @@
         </is>
       </c>
       <c r="E3" s="8" t="n">
-        <v>4371</v>
+        <v>4996</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="4">
@@ -3246,10 +3270,10 @@
         </is>
       </c>
       <c r="E4" s="8" t="n">
-        <v>3711</v>
+        <v>4235</v>
       </c>
       <c r="F4" s="9" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="5">
@@ -3268,10 +3292,10 @@
         </is>
       </c>
       <c r="E5" s="8" t="n">
-        <v>3575</v>
+        <v>4143</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="6">
@@ -3290,7 +3314,7 @@
         </is>
       </c>
       <c r="E6" s="8" t="n">
-        <v>3258</v>
+        <v>3742</v>
       </c>
       <c r="F6" s="9" t="n">
         <v>18.4</v>
@@ -3312,10 +3336,10 @@
         </is>
       </c>
       <c r="E7" s="8" t="n">
-        <v>1426</v>
+        <v>1661</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -3334,7 +3358,7 @@
         </is>
       </c>
       <c r="E8" s="8" t="n">
-        <v>1191</v>
+        <v>1366</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>6.7</v>
@@ -3356,7 +3380,7 @@
         </is>
       </c>
       <c r="E9" s="8" t="n">
-        <v>1133</v>
+        <v>1298</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>6.4</v>
@@ -3378,10 +3402,10 @@
         </is>
       </c>
       <c r="E10" s="8" t="n">
-        <v>11982</v>
+        <v>13709</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>67.7</v>
+        <v>67.59999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -3400,10 +3424,10 @@
         </is>
       </c>
       <c r="E11" s="8" t="n">
-        <v>4218</v>
+        <v>4787</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
     </row>
     <row r="12">
@@ -3422,10 +3446,10 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>3870</v>
+        <v>4416</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="13">
@@ -3444,10 +3468,10 @@
         </is>
       </c>
       <c r="E13" s="8" t="n">
-        <v>3608</v>
+        <v>4102</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="14">
@@ -3466,7 +3490,7 @@
         </is>
       </c>
       <c r="E14" s="8" t="n">
-        <v>3522</v>
+        <v>4037</v>
       </c>
       <c r="F14" s="9" t="n">
         <v>19.9</v>
@@ -3488,10 +3512,10 @@
         </is>
       </c>
       <c r="E15" s="8" t="n">
-        <v>3462</v>
+        <v>3874</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>19.6</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="16">
@@ -3510,10 +3534,10 @@
         </is>
       </c>
       <c r="E16" s="8" t="n">
-        <v>2633</v>
+        <v>2960</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>14.9</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="17">
@@ -3532,10 +3556,10 @@
         </is>
       </c>
       <c r="E17" s="8" t="n">
-        <v>2064</v>
+        <v>2359</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="18">
@@ -3558,7 +3582,7 @@
         </is>
       </c>
       <c r="E18" s="8" t="n">
-        <v>289</v>
+        <v>329</v>
       </c>
       <c r="F18" s="9" t="n">
         <v>1.6</v>
@@ -3584,7 +3608,7 @@
         </is>
       </c>
       <c r="E19" s="8" t="n">
-        <v>288</v>
+        <v>325</v>
       </c>
       <c r="F19" s="9" t="n">
         <v>1.6</v>
@@ -3610,7 +3634,7 @@
         </is>
       </c>
       <c r="E20" s="8" t="n">
-        <v>145</v>
+        <v>171</v>
       </c>
       <c r="F20" s="9" t="n">
         <v>0.8</v>
@@ -3636,10 +3660,10 @@
         </is>
       </c>
       <c r="E21" s="8" t="n">
-        <v>131</v>
+        <v>157</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="22">
@@ -3662,7 +3686,7 @@
         </is>
       </c>
       <c r="E22" s="8" t="n">
-        <v>123</v>
+        <v>143</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>0.7</v>
@@ -3688,7 +3712,7 @@
         </is>
       </c>
       <c r="E23" s="8" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>0.4</v>
@@ -3714,10 +3738,10 @@
         </is>
       </c>
       <c r="E24" s="8" t="n">
-        <v>8738</v>
+        <v>9936</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>49.4</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25">
@@ -3740,10 +3764,10 @@
         </is>
       </c>
       <c r="E25" s="8" t="n">
-        <v>3507</v>
+        <v>3969</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>19.8</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="26">
@@ -3766,10 +3790,10 @@
         </is>
       </c>
       <c r="E26" s="8" t="n">
-        <v>1597</v>
+        <v>1839</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="27">
@@ -3792,7 +3816,7 @@
         </is>
       </c>
       <c r="E27" s="8" t="n">
-        <v>1276</v>
+        <v>1456</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>7.2</v>
@@ -3818,10 +3842,10 @@
         </is>
       </c>
       <c r="E28" s="8" t="n">
-        <v>1135</v>
+        <v>1325</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="29">
@@ -3844,10 +3868,10 @@
         </is>
       </c>
       <c r="E29" s="8" t="n">
-        <v>628</v>
+        <v>727</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="30">
@@ -3870,7 +3894,7 @@
         </is>
       </c>
       <c r="E30" s="8" t="n">
-        <v>1666</v>
+        <v>1909</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>9.4</v>
@@ -3896,10 +3920,10 @@
         </is>
       </c>
       <c r="E31" s="8" t="n">
-        <v>1025</v>
+        <v>1159</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="32">
@@ -3922,10 +3946,10 @@
         </is>
       </c>
       <c r="E32" s="8" t="n">
-        <v>801</v>
+        <v>936</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="33">
@@ -3948,7 +3972,7 @@
         </is>
       </c>
       <c r="E33" s="8" t="n">
-        <v>774</v>
+        <v>893</v>
       </c>
       <c r="F33" s="9" t="n">
         <v>4.4</v>
@@ -3974,10 +3998,10 @@
         </is>
       </c>
       <c r="E34" s="8" t="n">
-        <v>576</v>
+        <v>639</v>
       </c>
       <c r="F34" s="9" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="35">
@@ -4000,10 +4024,10 @@
         </is>
       </c>
       <c r="E35" s="8" t="n">
-        <v>511</v>
+        <v>599</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -4026,10 +4050,10 @@
         </is>
       </c>
       <c r="E36" s="8" t="n">
-        <v>526</v>
+        <v>639</v>
       </c>
       <c r="F36" s="9" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="37">
@@ -4052,10 +4076,10 @@
         </is>
       </c>
       <c r="E37" s="8" t="n">
-        <v>411</v>
+        <v>498</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="38">
@@ -4078,7 +4102,7 @@
         </is>
       </c>
       <c r="E38" s="8" t="n">
-        <v>173</v>
+        <v>197</v>
       </c>
       <c r="F38" s="9" t="n">
         <v>1</v>
@@ -4104,7 +4128,7 @@
         </is>
       </c>
       <c r="E39" s="8" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F39" s="9" t="n">
         <v>0.3</v>
@@ -4130,10 +4154,10 @@
         </is>
       </c>
       <c r="E40" s="8" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="41">
@@ -4156,7 +4180,7 @@
         </is>
       </c>
       <c r="E41" s="8" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F41" s="9" t="n">
         <v>0.1</v>
@@ -4228,10 +4252,10 @@
         </is>
       </c>
       <c r="D2" s="8" t="n">
-        <v>183</v>
+        <v>212</v>
       </c>
       <c r="E2" s="9" t="n">
-        <v>74.40000000000001</v>
+        <v>74.09999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -4247,14 +4271,14 @@
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>60 a más años</t>
+          <t>18 a 59 años</t>
         </is>
       </c>
       <c r="D3" s="8" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>13</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="4">
@@ -4270,14 +4294,14 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>18 a 59 años</t>
+          <t>60 a más años</t>
         </is>
       </c>
       <c r="D4" s="8" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E4" s="9" t="n">
-        <v>12.6</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="5">
@@ -4297,10 +4321,10 @@
         </is>
       </c>
       <c r="D5" s="8" t="n">
-        <v>226</v>
+        <v>265</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>91.90000000000001</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="6">
@@ -4320,10 +4344,10 @@
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="7">
@@ -4346,7 +4370,7 @@
         <v>7</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="8">
@@ -4366,10 +4390,10 @@
         </is>
       </c>
       <c r="D8" s="8" t="n">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>50.8</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="9">
@@ -4389,10 +4413,10 @@
         </is>
       </c>
       <c r="D9" s="8" t="n">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>38.6</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="10">
@@ -4412,10 +4436,10 @@
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>10.6</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="11">
@@ -4435,10 +4459,10 @@
         </is>
       </c>
       <c r="D11" s="8" t="n">
-        <v>215</v>
+        <v>243</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>87.40000000000001</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12">
@@ -4458,10 +4482,10 @@
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>6.5</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="13">
@@ -4481,10 +4505,10 @@
         </is>
       </c>
       <c r="D13" s="8" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>6.1</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="14">
@@ -4504,10 +4528,10 @@
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>52.8</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="15">
@@ -4527,10 +4551,10 @@
         </is>
       </c>
       <c r="D15" s="8" t="n">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>30.9</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="16">
@@ -4550,10 +4574,10 @@
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>11.8</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="17">
@@ -4576,7 +4600,7 @@
         <v>11</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="18">
@@ -4596,10 +4620,10 @@
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>498</v>
+        <v>578</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>58.1</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="19">
@@ -4619,10 +4643,10 @@
         </is>
       </c>
       <c r="D19" s="8" t="n">
-        <v>254</v>
+        <v>284</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>29.6</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="20">
@@ -4642,10 +4666,10 @@
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>12.3</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="21">
@@ -4665,10 +4689,10 @@
         </is>
       </c>
       <c r="D21" s="8" t="n">
-        <v>734</v>
+        <v>846</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>85.59999999999999</v>
+        <v>85.7</v>
       </c>
     </row>
     <row r="22">
@@ -4688,10 +4712,10 @@
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>11.7</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="23">
@@ -4707,14 +4731,14 @@
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Divorciado/a</t>
+          <t>Viudo/a</t>
         </is>
       </c>
       <c r="D23" s="8" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="24">
@@ -4730,14 +4754,14 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Viudo/a</t>
+          <t>Divorciado/a</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="25">
@@ -4757,10 +4781,10 @@
         </is>
       </c>
       <c r="D25" s="8" t="n">
-        <v>400</v>
+        <v>464</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>46.7</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26">
@@ -4776,14 +4800,14 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Leve</t>
+          <t>Severo</t>
         </is>
       </c>
       <c r="D26" s="8" t="n">
-        <v>232</v>
+        <v>265</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>27.1</v>
+        <v>26.8</v>
       </c>
     </row>
     <row r="27">
@@ -4799,14 +4823,14 @@
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Severo</t>
+          <t>Leve</t>
         </is>
       </c>
       <c r="D27" s="8" t="n">
-        <v>225</v>
+        <v>258</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>26.3</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="28">
@@ -4826,7 +4850,7 @@
         </is>
       </c>
       <c r="D28" s="8" t="n">
-        <v>673</v>
+        <v>775</v>
       </c>
       <c r="E28" s="9" t="n">
         <v>78.5</v>
@@ -4849,10 +4873,10 @@
         </is>
       </c>
       <c r="D29" s="8" t="n">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>18.6</v>
+        <v>17.9</v>
       </c>
     </row>
     <row r="30">
@@ -4872,10 +4896,10 @@
         </is>
       </c>
       <c r="D30" s="8" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="31">
@@ -4895,10 +4919,10 @@
         </is>
       </c>
       <c r="D31" s="8" t="n">
-        <v>477</v>
+        <v>542</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>55.7</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="32">
@@ -4918,10 +4942,10 @@
         </is>
       </c>
       <c r="D32" s="8" t="n">
-        <v>329</v>
+        <v>383</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>38.4</v>
+        <v>38.8</v>
       </c>
     </row>
     <row r="33">
@@ -4941,10 +4965,10 @@
         </is>
       </c>
       <c r="D33" s="8" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="34">
@@ -4964,7 +4988,7 @@
         </is>
       </c>
       <c r="D34" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E34" s="9" t="n">
         <v>0.7</v>
@@ -4987,10 +5011,10 @@
         </is>
       </c>
       <c r="D35" s="8" t="n">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>68.8</v>
+        <v>68.5</v>
       </c>
     </row>
     <row r="36">
@@ -5006,14 +5030,14 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>60 a más años</t>
+          <t>18 a 59 años</t>
         </is>
       </c>
       <c r="D36" s="8" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E36" s="9" t="n">
-        <v>16.7</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="37">
@@ -5029,14 +5053,14 @@
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>18 a 59 años</t>
+          <t>60 a más años</t>
         </is>
       </c>
       <c r="D37" s="8" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>14.5</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="38">
@@ -5056,10 +5080,10 @@
         </is>
       </c>
       <c r="D38" s="8" t="n">
-        <v>196</v>
+        <v>214</v>
       </c>
       <c r="E38" s="9" t="n">
-        <v>88.7</v>
+        <v>88.8</v>
       </c>
     </row>
     <row r="39">
@@ -5079,10 +5103,10 @@
         </is>
       </c>
       <c r="D39" s="8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="40">
@@ -5105,7 +5129,7 @@
         <v>7</v>
       </c>
       <c r="E40" s="9" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="41">
@@ -5128,7 +5152,7 @@
         <v>1</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="42">
@@ -5148,7 +5172,7 @@
         </is>
       </c>
       <c r="D42" s="8" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="E42" s="9" t="n">
         <v>40.7</v>
@@ -5171,10 +5195,10 @@
         </is>
       </c>
       <c r="D43" s="8" t="n">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v>39.4</v>
+        <v>40.2</v>
       </c>
     </row>
     <row r="44">
@@ -5194,10 +5218,10 @@
         </is>
       </c>
       <c r="D44" s="8" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E44" s="9" t="n">
-        <v>19.9</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="45">
@@ -5217,7 +5241,7 @@
         </is>
       </c>
       <c r="D45" s="8" t="n">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="E45" s="9" t="n">
         <v>85.09999999999999</v>
@@ -5240,10 +5264,10 @@
         </is>
       </c>
       <c r="D46" s="8" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E46" s="9" t="n">
-        <v>12.2</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="47">
@@ -5266,7 +5290,7 @@
         <v>6</v>
       </c>
       <c r="E47" s="9" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="48">
@@ -5286,10 +5310,10 @@
         </is>
       </c>
       <c r="D48" s="8" t="n">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="E48" s="9" t="n">
-        <v>59.3</v>
+        <v>60.2</v>
       </c>
     </row>
     <row r="49">
@@ -5309,10 +5333,10 @@
         </is>
       </c>
       <c r="D49" s="8" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E49" s="9" t="n">
-        <v>35.3</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="50">
@@ -5335,7 +5359,7 @@
         <v>7</v>
       </c>
       <c r="E50" s="9" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="51">
@@ -5355,10 +5379,10 @@
         </is>
       </c>
       <c r="D51" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E51" s="9" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="52">
@@ -5378,10 +5402,10 @@
         </is>
       </c>
       <c r="D52" s="8" t="n">
-        <v>1512</v>
+        <v>1720</v>
       </c>
       <c r="E52" s="9" t="n">
-        <v>72.5</v>
+        <v>72.09999999999999</v>
       </c>
     </row>
     <row r="53">
@@ -5401,10 +5425,10 @@
         </is>
       </c>
       <c r="D53" s="8" t="n">
-        <v>317</v>
+        <v>372</v>
       </c>
       <c r="E53" s="9" t="n">
-        <v>15.2</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="54">
@@ -5424,10 +5448,10 @@
         </is>
       </c>
       <c r="D54" s="8" t="n">
-        <v>257</v>
+        <v>292</v>
       </c>
       <c r="E54" s="9" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="55">
@@ -5447,10 +5471,10 @@
         </is>
       </c>
       <c r="D55" s="8" t="n">
-        <v>1854</v>
+        <v>2101</v>
       </c>
       <c r="E55" s="9" t="n">
-        <v>88.90000000000001</v>
+        <v>88.09999999999999</v>
       </c>
     </row>
     <row r="56">
@@ -5470,10 +5494,10 @@
         </is>
       </c>
       <c r="D56" s="8" t="n">
-        <v>166</v>
+        <v>206</v>
       </c>
       <c r="E56" s="9" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="57">
@@ -5493,7 +5517,7 @@
         </is>
       </c>
       <c r="D57" s="8" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E57" s="9" t="n">
         <v>1.9</v>
@@ -5516,10 +5540,10 @@
         </is>
       </c>
       <c r="D58" s="8" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E58" s="9" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="59">
@@ -5539,10 +5563,10 @@
         </is>
       </c>
       <c r="D59" s="8" t="n">
-        <v>1189</v>
+        <v>1365</v>
       </c>
       <c r="E59" s="9" t="n">
-        <v>57</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="60">
@@ -5562,10 +5586,10 @@
         </is>
       </c>
       <c r="D60" s="8" t="n">
-        <v>640</v>
+        <v>715</v>
       </c>
       <c r="E60" s="9" t="n">
-        <v>30.7</v>
+        <v>30</v>
       </c>
     </row>
     <row r="61">
@@ -5585,10 +5609,10 @@
         </is>
       </c>
       <c r="D61" s="8" t="n">
-        <v>257</v>
+        <v>304</v>
       </c>
       <c r="E61" s="9" t="n">
-        <v>12.3</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="62">
@@ -5608,10 +5632,10 @@
         </is>
       </c>
       <c r="D62" s="8" t="n">
-        <v>1840</v>
+        <v>2108</v>
       </c>
       <c r="E62" s="9" t="n">
-        <v>88.2</v>
+        <v>88.40000000000001</v>
       </c>
     </row>
     <row r="63">
@@ -5631,7 +5655,7 @@
         </is>
       </c>
       <c r="D63" s="8" t="n">
-        <v>186</v>
+        <v>212</v>
       </c>
       <c r="E63" s="9" t="n">
         <v>8.9</v>
@@ -5654,10 +5678,10 @@
         </is>
       </c>
       <c r="D64" s="8" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E64" s="9" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="65">
@@ -5677,10 +5701,10 @@
         </is>
       </c>
       <c r="D65" s="8" t="n">
-        <v>1392</v>
+        <v>1582</v>
       </c>
       <c r="E65" s="9" t="n">
-        <v>66.7</v>
+        <v>66.40000000000001</v>
       </c>
     </row>
     <row r="66">
@@ -5700,10 +5724,10 @@
         </is>
       </c>
       <c r="D66" s="8" t="n">
-        <v>605</v>
+        <v>704</v>
       </c>
       <c r="E66" s="9" t="n">
-        <v>29</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="67">
@@ -5723,10 +5747,10 @@
         </is>
       </c>
       <c r="D67" s="8" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="E67" s="9" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="68">
@@ -5746,7 +5770,7 @@
         </is>
       </c>
       <c r="D68" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E68" s="9" t="n">
         <v>0.3</v>
@@ -5769,10 +5793,10 @@
         </is>
       </c>
       <c r="D69" s="8" t="n">
-        <v>416</v>
+        <v>470</v>
       </c>
       <c r="E69" s="9" t="n">
-        <v>81.59999999999999</v>
+        <v>81.90000000000001</v>
       </c>
     </row>
     <row r="70">
@@ -5792,10 +5816,10 @@
         </is>
       </c>
       <c r="D70" s="8" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E70" s="9" t="n">
-        <v>10.2</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="71">
@@ -5815,7 +5839,7 @@
         </is>
       </c>
       <c r="D71" s="8" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E71" s="9" t="n">
         <v>8.199999999999999</v>
@@ -5838,10 +5862,10 @@
         </is>
       </c>
       <c r="D72" s="8" t="n">
-        <v>461</v>
+        <v>522</v>
       </c>
       <c r="E72" s="9" t="n">
-        <v>90.40000000000001</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="73">
@@ -5861,10 +5885,10 @@
         </is>
       </c>
       <c r="D73" s="8" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E73" s="9" t="n">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="74">
@@ -5884,7 +5908,7 @@
         </is>
       </c>
       <c r="D74" s="8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E74" s="9" t="n">
         <v>1.6</v>
@@ -5930,10 +5954,10 @@
         </is>
       </c>
       <c r="D76" s="8" t="n">
-        <v>244</v>
+        <v>286</v>
       </c>
       <c r="E76" s="9" t="n">
-        <v>47.8</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="77">
@@ -5953,10 +5977,10 @@
         </is>
       </c>
       <c r="D77" s="8" t="n">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="E77" s="9" t="n">
-        <v>26.5</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="78">
@@ -5976,10 +6000,10 @@
         </is>
       </c>
       <c r="D78" s="8" t="n">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="E78" s="9" t="n">
-        <v>25.7</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="79">
@@ -5999,10 +6023,10 @@
         </is>
       </c>
       <c r="D79" s="8" t="n">
-        <v>477</v>
+        <v>537</v>
       </c>
       <c r="E79" s="9" t="n">
-        <v>93.5</v>
+        <v>93.59999999999999</v>
       </c>
     </row>
     <row r="80">
@@ -6022,7 +6046,7 @@
         </is>
       </c>
       <c r="D80" s="8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E80" s="9" t="n">
         <v>3.3</v>
@@ -6045,7 +6069,7 @@
         </is>
       </c>
       <c r="D81" s="8" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E81" s="9" t="n">
         <v>3.1</v>
@@ -6068,10 +6092,10 @@
         </is>
       </c>
       <c r="D82" s="8" t="n">
-        <v>268</v>
+        <v>310</v>
       </c>
       <c r="E82" s="9" t="n">
-        <v>52.5</v>
+        <v>54</v>
       </c>
     </row>
     <row r="83">
@@ -6091,10 +6115,10 @@
         </is>
       </c>
       <c r="D83" s="8" t="n">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="E83" s="9" t="n">
-        <v>39.6</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="84">
@@ -6114,7 +6138,7 @@
         </is>
       </c>
       <c r="D84" s="8" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E84" s="9" t="n">
         <v>4.5</v>
@@ -6137,10 +6161,10 @@
         </is>
       </c>
       <c r="D85" s="8" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E85" s="9" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="86">
@@ -6160,10 +6184,10 @@
         </is>
       </c>
       <c r="D86" s="8" t="n">
-        <v>243</v>
+        <v>275</v>
       </c>
       <c r="E86" s="9" t="n">
-        <v>67.5</v>
+        <v>66.3</v>
       </c>
     </row>
     <row r="87">
@@ -6183,10 +6207,10 @@
         </is>
       </c>
       <c r="D87" s="8" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="E87" s="9" t="n">
-        <v>22.2</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="88">
@@ -6206,10 +6230,10 @@
         </is>
       </c>
       <c r="D88" s="8" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="E88" s="9" t="n">
-        <v>10.3</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="89">
@@ -6229,10 +6253,10 @@
         </is>
       </c>
       <c r="D89" s="8" t="n">
-        <v>324</v>
+        <v>363</v>
       </c>
       <c r="E89" s="9" t="n">
-        <v>90</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="90">
@@ -6252,10 +6276,10 @@
         </is>
       </c>
       <c r="D90" s="8" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E90" s="9" t="n">
-        <v>7.5</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="91">
@@ -6275,7 +6299,7 @@
         </is>
       </c>
       <c r="D91" s="8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E91" s="9" t="n">
         <v>2.2</v>
@@ -6301,7 +6325,7 @@
         <v>1</v>
       </c>
       <c r="E92" s="9" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="93">
@@ -6321,10 +6345,10 @@
         </is>
       </c>
       <c r="D93" s="8" t="n">
-        <v>183</v>
+        <v>203</v>
       </c>
       <c r="E93" s="9" t="n">
-        <v>50.8</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="94">
@@ -6344,10 +6368,10 @@
         </is>
       </c>
       <c r="D94" s="8" t="n">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="E94" s="9" t="n">
-        <v>33.1</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="95">
@@ -6367,10 +6391,10 @@
         </is>
       </c>
       <c r="D95" s="8" t="n">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="E95" s="9" t="n">
-        <v>16.1</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="96">
@@ -6390,10 +6414,10 @@
         </is>
       </c>
       <c r="D96" s="8" t="n">
-        <v>316</v>
+        <v>367</v>
       </c>
       <c r="E96" s="9" t="n">
-        <v>87.8</v>
+        <v>88.40000000000001</v>
       </c>
     </row>
     <row r="97">
@@ -6413,10 +6437,10 @@
         </is>
       </c>
       <c r="D97" s="8" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E97" s="9" t="n">
-        <v>8.6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="98">
@@ -6436,10 +6460,10 @@
         </is>
       </c>
       <c r="D98" s="8" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E98" s="9" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="99">
@@ -6459,10 +6483,10 @@
         </is>
       </c>
       <c r="D99" s="8" t="n">
-        <v>186</v>
+        <v>217</v>
       </c>
       <c r="E99" s="9" t="n">
-        <v>51.7</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="100">
@@ -6482,10 +6506,10 @@
         </is>
       </c>
       <c r="D100" s="8" t="n">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="E100" s="9" t="n">
-        <v>40.3</v>
+        <v>39</v>
       </c>
     </row>
     <row r="101">
@@ -6505,10 +6529,10 @@
         </is>
       </c>
       <c r="D101" s="8" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="E101" s="9" t="n">
-        <v>8.1</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="102">
@@ -6528,10 +6552,10 @@
         </is>
       </c>
       <c r="D102" s="8" t="n">
-        <v>373</v>
+        <v>436</v>
       </c>
       <c r="E102" s="9" t="n">
-        <v>55.3</v>
+        <v>57</v>
       </c>
     </row>
     <row r="103">
@@ -6551,10 +6575,10 @@
         </is>
       </c>
       <c r="D103" s="8" t="n">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="E103" s="9" t="n">
-        <v>24</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="104">
@@ -6574,10 +6598,10 @@
         </is>
       </c>
       <c r="D104" s="8" t="n">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="E104" s="9" t="n">
-        <v>20.6</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="105">
@@ -6597,10 +6621,10 @@
         </is>
       </c>
       <c r="D105" s="8" t="n">
-        <v>533</v>
+        <v>611</v>
       </c>
       <c r="E105" s="9" t="n">
-        <v>79.09999999999999</v>
+        <v>79.90000000000001</v>
       </c>
     </row>
     <row r="106">
@@ -6620,10 +6644,10 @@
         </is>
       </c>
       <c r="D106" s="8" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="E106" s="9" t="n">
-        <v>15.4</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="107">
@@ -6643,10 +6667,10 @@
         </is>
       </c>
       <c r="D107" s="8" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E107" s="9" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="108">
@@ -6666,10 +6690,10 @@
         </is>
       </c>
       <c r="D108" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E108" s="9" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -6689,10 +6713,10 @@
         </is>
       </c>
       <c r="D109" s="8" t="n">
-        <v>341</v>
+        <v>398</v>
       </c>
       <c r="E109" s="9" t="n">
-        <v>50.6</v>
+        <v>52</v>
       </c>
     </row>
     <row r="110">
@@ -6712,10 +6736,10 @@
         </is>
       </c>
       <c r="D110" s="8" t="n">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="E110" s="9" t="n">
-        <v>29.4</v>
+        <v>27.7</v>
       </c>
     </row>
     <row r="111">
@@ -6735,10 +6759,10 @@
         </is>
       </c>
       <c r="D111" s="8" t="n">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="E111" s="9" t="n">
-        <v>20</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="112">
@@ -6758,10 +6782,10 @@
         </is>
       </c>
       <c r="D112" s="8" t="n">
-        <v>545</v>
+        <v>620</v>
       </c>
       <c r="E112" s="9" t="n">
-        <v>80.90000000000001</v>
+        <v>81</v>
       </c>
     </row>
     <row r="113">
@@ -6781,7 +6805,7 @@
         </is>
       </c>
       <c r="D113" s="8" t="n">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="E113" s="9" t="n">
         <v>15</v>
@@ -6804,10 +6828,10 @@
         </is>
       </c>
       <c r="D114" s="8" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E114" s="9" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="115">
@@ -6827,10 +6851,10 @@
         </is>
       </c>
       <c r="D115" s="8" t="n">
-        <v>384</v>
+        <v>427</v>
       </c>
       <c r="E115" s="9" t="n">
-        <v>57</v>
+        <v>55.8</v>
       </c>
     </row>
     <row r="116">
@@ -6850,10 +6874,10 @@
         </is>
       </c>
       <c r="D116" s="8" t="n">
-        <v>250</v>
+        <v>294</v>
       </c>
       <c r="E116" s="9" t="n">
-        <v>37.1</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="117">
@@ -6873,10 +6897,10 @@
         </is>
       </c>
       <c r="D117" s="8" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E117" s="9" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="118">
@@ -6919,10 +6943,10 @@
         </is>
       </c>
       <c r="D119" s="8" t="n">
-        <v>851</v>
+        <v>953</v>
       </c>
       <c r="E119" s="9" t="n">
-        <v>75</v>
+        <v>74.7</v>
       </c>
     </row>
     <row r="120">
@@ -6942,10 +6966,10 @@
         </is>
       </c>
       <c r="D120" s="8" t="n">
-        <v>183</v>
+        <v>210</v>
       </c>
       <c r="E120" s="9" t="n">
-        <v>16.1</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="121">
@@ -6965,7 +6989,7 @@
         </is>
       </c>
       <c r="D121" s="8" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="E121" s="9" t="n">
         <v>8.800000000000001</v>
@@ -6988,10 +7012,10 @@
         </is>
       </c>
       <c r="D122" s="8" t="n">
-        <v>1041</v>
+        <v>1172</v>
       </c>
       <c r="E122" s="9" t="n">
-        <v>91.8</v>
+        <v>91.90000000000001</v>
       </c>
     </row>
     <row r="123">
@@ -7011,7 +7035,7 @@
         </is>
       </c>
       <c r="D123" s="8" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="E123" s="9" t="n">
         <v>6.2</v>
@@ -7034,10 +7058,10 @@
         </is>
       </c>
       <c r="D124" s="8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E124" s="9" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="125">
@@ -7080,10 +7104,10 @@
         </is>
       </c>
       <c r="D126" s="8" t="n">
-        <v>554</v>
+        <v>617</v>
       </c>
       <c r="E126" s="9" t="n">
-        <v>48.9</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="127">
@@ -7103,10 +7127,10 @@
         </is>
       </c>
       <c r="D127" s="8" t="n">
-        <v>505</v>
+        <v>572</v>
       </c>
       <c r="E127" s="9" t="n">
-        <v>44.5</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="128">
@@ -7126,10 +7150,10 @@
         </is>
       </c>
       <c r="D128" s="8" t="n">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="E128" s="9" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="129">
@@ -7149,10 +7173,10 @@
         </is>
       </c>
       <c r="D129" s="8" t="n">
-        <v>1002</v>
+        <v>1121</v>
       </c>
       <c r="E129" s="9" t="n">
-        <v>88.40000000000001</v>
+        <v>87.90000000000001</v>
       </c>
     </row>
     <row r="130">
@@ -7172,10 +7196,10 @@
         </is>
       </c>
       <c r="D130" s="8" t="n">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="E130" s="9" t="n">
-        <v>8.5</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="131">
@@ -7195,7 +7219,7 @@
         </is>
       </c>
       <c r="D131" s="8" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E131" s="9" t="n">
         <v>3.2</v>
@@ -7218,7 +7242,7 @@
         </is>
       </c>
       <c r="D132" s="8" t="n">
-        <v>756</v>
+        <v>851</v>
       </c>
       <c r="E132" s="9" t="n">
         <v>66.7</v>
@@ -7241,10 +7265,10 @@
         </is>
       </c>
       <c r="D133" s="8" t="n">
-        <v>314</v>
+        <v>354</v>
       </c>
       <c r="E133" s="9" t="n">
-        <v>27.7</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="134">
@@ -7264,7 +7288,7 @@
         </is>
       </c>
       <c r="D134" s="8" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="E134" s="9" t="n">
         <v>4.9</v>
@@ -7290,7 +7314,7 @@
         <v>8</v>
       </c>
       <c r="E135" s="9" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="136">
@@ -7310,10 +7334,10 @@
         </is>
       </c>
       <c r="D136" s="8" t="n">
-        <v>237</v>
+        <v>279</v>
       </c>
       <c r="E136" s="9" t="n">
-        <v>83.7</v>
+        <v>84</v>
       </c>
     </row>
     <row r="137">
@@ -7333,7 +7357,7 @@
         </is>
       </c>
       <c r="D137" s="8" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E137" s="9" t="n">
         <v>9.9</v>
@@ -7356,10 +7380,10 @@
         </is>
       </c>
       <c r="D138" s="8" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E138" s="9" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="139">
@@ -7379,10 +7403,10 @@
         </is>
       </c>
       <c r="D139" s="8" t="n">
-        <v>259</v>
+        <v>306</v>
       </c>
       <c r="E139" s="9" t="n">
-        <v>91.5</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="140">
@@ -7402,10 +7426,10 @@
         </is>
       </c>
       <c r="D140" s="8" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E140" s="9" t="n">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="141">
@@ -7428,7 +7452,7 @@
         <v>1</v>
       </c>
       <c r="E141" s="9" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="142">
@@ -7448,10 +7472,10 @@
         </is>
       </c>
       <c r="D142" s="8" t="n">
-        <v>143</v>
+        <v>167</v>
       </c>
       <c r="E142" s="9" t="n">
-        <v>50.5</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="143">
@@ -7471,10 +7495,10 @@
         </is>
       </c>
       <c r="D143" s="8" t="n">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="E143" s="9" t="n">
-        <v>37.1</v>
+        <v>37</v>
       </c>
     </row>
     <row r="144">
@@ -7494,10 +7518,10 @@
         </is>
       </c>
       <c r="D144" s="8" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="E144" s="9" t="n">
-        <v>12.4</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="145">
@@ -7517,10 +7541,10 @@
         </is>
       </c>
       <c r="D145" s="8" t="n">
-        <v>267</v>
+        <v>311</v>
       </c>
       <c r="E145" s="9" t="n">
-        <v>94.3</v>
+        <v>93.7</v>
       </c>
     </row>
     <row r="146">
@@ -7540,10 +7564,10 @@
         </is>
       </c>
       <c r="D146" s="8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E146" s="9" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="147">
@@ -7563,10 +7587,10 @@
         </is>
       </c>
       <c r="D147" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E147" s="9" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="148">
@@ -7586,10 +7610,10 @@
         </is>
       </c>
       <c r="D148" s="8" t="n">
-        <v>213</v>
+        <v>254</v>
       </c>
       <c r="E148" s="9" t="n">
-        <v>75.3</v>
+        <v>76.5</v>
       </c>
     </row>
     <row r="149">
@@ -7609,10 +7633,10 @@
         </is>
       </c>
       <c r="D149" s="8" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E149" s="9" t="n">
-        <v>23.7</v>
+        <v>21.1</v>
       </c>
     </row>
     <row r="150">
@@ -7632,10 +7656,10 @@
         </is>
       </c>
       <c r="D150" s="8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E150" s="9" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="151">
@@ -7658,7 +7682,7 @@
         <v>1</v>
       </c>
       <c r="E151" s="9" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="152">
@@ -7678,10 +7702,10 @@
         </is>
       </c>
       <c r="D152" s="8" t="n">
-        <v>396</v>
+        <v>456</v>
       </c>
       <c r="E152" s="9" t="n">
-        <v>79.5</v>
+        <v>78.59999999999999</v>
       </c>
     </row>
     <row r="153">
@@ -7701,10 +7725,10 @@
         </is>
       </c>
       <c r="D153" s="8" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="E153" s="9" t="n">
-        <v>12.7</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="154">
@@ -7724,10 +7748,10 @@
         </is>
       </c>
       <c r="D154" s="8" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="E154" s="9" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="155">
@@ -7747,10 +7771,10 @@
         </is>
       </c>
       <c r="D155" s="8" t="n">
-        <v>468</v>
+        <v>542</v>
       </c>
       <c r="E155" s="9" t="n">
-        <v>94</v>
+        <v>93.40000000000001</v>
       </c>
     </row>
     <row r="156">
@@ -7770,10 +7794,10 @@
         </is>
       </c>
       <c r="D156" s="8" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E156" s="9" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="157">
@@ -7789,14 +7813,14 @@
       </c>
       <c r="C157" s="7" t="inlineStr">
         <is>
-          <t>Divorciado/a</t>
+          <t>Viudo/a</t>
         </is>
       </c>
       <c r="D157" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E157" s="9" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="158">
@@ -7812,14 +7836,14 @@
       </c>
       <c r="C158" s="7" t="inlineStr">
         <is>
-          <t>Viudo/a</t>
+          <t>Divorciado/a</t>
         </is>
       </c>
       <c r="D158" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E158" s="9" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="159">
@@ -7839,10 +7863,10 @@
         </is>
       </c>
       <c r="D159" s="8" t="n">
-        <v>258</v>
+        <v>301</v>
       </c>
       <c r="E159" s="9" t="n">
-        <v>51.8</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="160">
@@ -7862,10 +7886,10 @@
         </is>
       </c>
       <c r="D160" s="8" t="n">
-        <v>183</v>
+        <v>212</v>
       </c>
       <c r="E160" s="9" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="161">
@@ -7885,10 +7909,10 @@
         </is>
       </c>
       <c r="D161" s="8" t="n">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="E161" s="9" t="n">
-        <v>11.4</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="162">
@@ -7908,10 +7932,10 @@
         </is>
       </c>
       <c r="D162" s="8" t="n">
-        <v>438</v>
+        <v>501</v>
       </c>
       <c r="E162" s="9" t="n">
-        <v>88</v>
+        <v>86.40000000000001</v>
       </c>
     </row>
     <row r="163">
@@ -7927,14 +7951,14 @@
       </c>
       <c r="C163" s="7" t="inlineStr">
         <is>
-          <t>Vínculo relacional de pareja</t>
+          <t>Sin vínculo relacional de pareja ni familiar</t>
         </is>
       </c>
       <c r="D163" s="8" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="E163" s="9" t="n">
-        <v>6</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="164">
@@ -7950,14 +7974,14 @@
       </c>
       <c r="C164" s="7" t="inlineStr">
         <is>
-          <t>Sin vínculo relacional de pareja ni familiar</t>
+          <t>Vínculo relacional de pareja</t>
         </is>
       </c>
       <c r="D164" s="8" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E164" s="9" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="165">
@@ -7977,10 +8001,10 @@
         </is>
       </c>
       <c r="D165" s="8" t="n">
-        <v>272</v>
+        <v>321</v>
       </c>
       <c r="E165" s="9" t="n">
-        <v>54.6</v>
+        <v>55.3</v>
       </c>
     </row>
     <row r="166">
@@ -8000,10 +8024,10 @@
         </is>
       </c>
       <c r="D166" s="8" t="n">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="E166" s="9" t="n">
-        <v>36.5</v>
+        <v>35</v>
       </c>
     </row>
     <row r="167">
@@ -8023,10 +8047,10 @@
         </is>
       </c>
       <c r="D167" s="8" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E167" s="9" t="n">
-        <v>8.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="168">
@@ -8046,10 +8070,10 @@
         </is>
       </c>
       <c r="D168" s="8" t="n">
-        <v>457</v>
+        <v>512</v>
       </c>
       <c r="E168" s="9" t="n">
-        <v>71</v>
+        <v>70.90000000000001</v>
       </c>
     </row>
     <row r="169">
@@ -8069,10 +8093,10 @@
         </is>
       </c>
       <c r="D169" s="8" t="n">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="E169" s="9" t="n">
-        <v>17.5</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="170">
@@ -8092,10 +8116,10 @@
         </is>
       </c>
       <c r="D170" s="8" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="E170" s="9" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="171">
@@ -8115,10 +8139,10 @@
         </is>
       </c>
       <c r="D171" s="8" t="n">
-        <v>565</v>
+        <v>632</v>
       </c>
       <c r="E171" s="9" t="n">
-        <v>87.7</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="172">
@@ -8138,10 +8162,10 @@
         </is>
       </c>
       <c r="D172" s="8" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E172" s="9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="173">
@@ -8161,10 +8185,10 @@
         </is>
       </c>
       <c r="D173" s="8" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E173" s="9" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="174">
@@ -8184,10 +8208,10 @@
         </is>
       </c>
       <c r="D174" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E174" s="9" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="175">
@@ -8207,10 +8231,10 @@
         </is>
       </c>
       <c r="D175" s="8" t="n">
-        <v>272</v>
+        <v>303</v>
       </c>
       <c r="E175" s="9" t="n">
-        <v>42.2</v>
+        <v>42</v>
       </c>
     </row>
     <row r="176">
@@ -8230,10 +8254,10 @@
         </is>
       </c>
       <c r="D176" s="8" t="n">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="E176" s="9" t="n">
-        <v>30.7</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="177">
@@ -8253,10 +8277,10 @@
         </is>
       </c>
       <c r="D177" s="8" t="n">
-        <v>174</v>
+        <v>206</v>
       </c>
       <c r="E177" s="9" t="n">
-        <v>27</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="178">
@@ -8276,10 +8300,10 @@
         </is>
       </c>
       <c r="D178" s="8" t="n">
-        <v>540</v>
+        <v>597</v>
       </c>
       <c r="E178" s="9" t="n">
-        <v>83.90000000000001</v>
+        <v>82.7</v>
       </c>
     </row>
     <row r="179">
@@ -8299,10 +8323,10 @@
         </is>
       </c>
       <c r="D179" s="8" t="n">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="E179" s="9" t="n">
-        <v>11.5</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="180">
@@ -8322,10 +8346,10 @@
         </is>
       </c>
       <c r="D180" s="8" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E180" s="9" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="181">
@@ -8345,10 +8369,10 @@
         </is>
       </c>
       <c r="D181" s="8" t="n">
-        <v>299</v>
+        <v>347</v>
       </c>
       <c r="E181" s="9" t="n">
-        <v>46.4</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="182">
@@ -8368,10 +8392,10 @@
         </is>
       </c>
       <c r="D182" s="8" t="n">
-        <v>284</v>
+        <v>307</v>
       </c>
       <c r="E182" s="9" t="n">
-        <v>44.1</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="183">
@@ -8391,7 +8415,7 @@
         </is>
       </c>
       <c r="D183" s="8" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="E183" s="9" t="n">
         <v>9</v>
@@ -8417,7 +8441,7 @@
         <v>3</v>
       </c>
       <c r="E184" s="9" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="185">
@@ -8437,10 +8461,10 @@
         </is>
       </c>
       <c r="D185" s="8" t="n">
-        <v>549</v>
+        <v>621</v>
       </c>
       <c r="E185" s="9" t="n">
-        <v>74.90000000000001</v>
+        <v>75.3</v>
       </c>
     </row>
     <row r="186">
@@ -8460,10 +8484,10 @@
         </is>
       </c>
       <c r="D186" s="8" t="n">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="E186" s="9" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="187">
@@ -8483,10 +8507,10 @@
         </is>
       </c>
       <c r="D187" s="8" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E187" s="9" t="n">
-        <v>11.1</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="188">
@@ -8506,10 +8530,10 @@
         </is>
       </c>
       <c r="D188" s="8" t="n">
-        <v>656</v>
+        <v>739</v>
       </c>
       <c r="E188" s="9" t="n">
-        <v>89.5</v>
+        <v>89.59999999999999</v>
       </c>
     </row>
     <row r="189">
@@ -8529,10 +8553,10 @@
         </is>
       </c>
       <c r="D189" s="8" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E189" s="9" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="190">
@@ -8552,7 +8576,7 @@
         </is>
       </c>
       <c r="D190" s="8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E190" s="9" t="n">
         <v>1.9</v>
@@ -8578,7 +8602,7 @@
         <v>2</v>
       </c>
       <c r="E191" s="9" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="192">
@@ -8598,10 +8622,10 @@
         </is>
       </c>
       <c r="D192" s="8" t="n">
-        <v>353</v>
+        <v>391</v>
       </c>
       <c r="E192" s="9" t="n">
-        <v>48.2</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="193">
@@ -8621,10 +8645,10 @@
         </is>
       </c>
       <c r="D193" s="8" t="n">
-        <v>290</v>
+        <v>330</v>
       </c>
       <c r="E193" s="9" t="n">
-        <v>39.6</v>
+        <v>40</v>
       </c>
     </row>
     <row r="194">
@@ -8644,10 +8668,10 @@
         </is>
       </c>
       <c r="D194" s="8" t="n">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="E194" s="9" t="n">
-        <v>12.3</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="195">
@@ -8667,10 +8691,10 @@
         </is>
       </c>
       <c r="D195" s="8" t="n">
-        <v>642</v>
+        <v>725</v>
       </c>
       <c r="E195" s="9" t="n">
-        <v>87.59999999999999</v>
+        <v>87.90000000000001</v>
       </c>
     </row>
     <row r="196">
@@ -8690,10 +8714,10 @@
         </is>
       </c>
       <c r="D196" s="8" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E196" s="9" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
     </row>
     <row r="197">
@@ -8713,10 +8737,10 @@
         </is>
       </c>
       <c r="D197" s="8" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E197" s="9" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="198">
@@ -8736,10 +8760,10 @@
         </is>
       </c>
       <c r="D198" s="8" t="n">
-        <v>427</v>
+        <v>485</v>
       </c>
       <c r="E198" s="9" t="n">
-        <v>58.3</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="199">
@@ -8759,10 +8783,10 @@
         </is>
       </c>
       <c r="D199" s="8" t="n">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="E199" s="9" t="n">
-        <v>33.8</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="200">
@@ -8782,7 +8806,7 @@
         </is>
       </c>
       <c r="D200" s="8" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E200" s="9" t="n">
         <v>7.2</v>
@@ -8808,7 +8832,7 @@
         <v>5</v>
       </c>
       <c r="E201" s="9" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="202">
@@ -8828,10 +8852,10 @@
         </is>
       </c>
       <c r="D202" s="8" t="n">
-        <v>741</v>
+        <v>855</v>
       </c>
       <c r="E202" s="9" t="n">
-        <v>77</v>
+        <v>75.3</v>
       </c>
     </row>
     <row r="203">
@@ -8851,10 +8875,10 @@
         </is>
       </c>
       <c r="D203" s="8" t="n">
-        <v>119</v>
+        <v>149</v>
       </c>
       <c r="E203" s="9" t="n">
-        <v>12.4</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="204">
@@ -8874,10 +8898,10 @@
         </is>
       </c>
       <c r="D204" s="8" t="n">
-        <v>102</v>
+        <v>132</v>
       </c>
       <c r="E204" s="9" t="n">
-        <v>10.6</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="205">
@@ -8897,10 +8921,10 @@
         </is>
       </c>
       <c r="D205" s="8" t="n">
-        <v>894</v>
+        <v>1039</v>
       </c>
       <c r="E205" s="9" t="n">
-        <v>92.90000000000001</v>
+        <v>91.5</v>
       </c>
     </row>
     <row r="206">
@@ -8920,10 +8944,10 @@
         </is>
       </c>
       <c r="D206" s="8" t="n">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="E206" s="9" t="n">
-        <v>5.3</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="207">
@@ -8943,10 +8967,10 @@
         </is>
       </c>
       <c r="D207" s="8" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E207" s="9" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="208">
@@ -8966,10 +8990,10 @@
         </is>
       </c>
       <c r="D208" s="8" t="n">
-        <v>362</v>
+        <v>438</v>
       </c>
       <c r="E208" s="9" t="n">
-        <v>37.6</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="209">
@@ -8985,14 +9009,14 @@
       </c>
       <c r="C209" s="7" t="inlineStr">
         <is>
-          <t>Leve</t>
+          <t>Severo</t>
         </is>
       </c>
       <c r="D209" s="8" t="n">
-        <v>302</v>
+        <v>352</v>
       </c>
       <c r="E209" s="9" t="n">
-        <v>31.4</v>
+        <v>31</v>
       </c>
     </row>
     <row r="210">
@@ -9008,14 +9032,14 @@
       </c>
       <c r="C210" s="7" t="inlineStr">
         <is>
-          <t>Severo</t>
+          <t>Leve</t>
         </is>
       </c>
       <c r="D210" s="8" t="n">
-        <v>298</v>
+        <v>346</v>
       </c>
       <c r="E210" s="9" t="n">
-        <v>31</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="211">
@@ -9035,10 +9059,10 @@
         </is>
       </c>
       <c r="D211" s="8" t="n">
-        <v>858</v>
+        <v>1011</v>
       </c>
       <c r="E211" s="9" t="n">
-        <v>89.2</v>
+        <v>89</v>
       </c>
     </row>
     <row r="212">
@@ -9058,10 +9082,10 @@
         </is>
       </c>
       <c r="D212" s="8" t="n">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="E212" s="9" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="213">
@@ -9081,7 +9105,7 @@
         </is>
       </c>
       <c r="D213" s="8" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E213" s="9" t="n">
         <v>3.4</v>
@@ -9104,10 +9128,10 @@
         </is>
       </c>
       <c r="D214" s="8" t="n">
-        <v>540</v>
+        <v>639</v>
       </c>
       <c r="E214" s="9" t="n">
-        <v>56.1</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="215">
@@ -9127,10 +9151,10 @@
         </is>
       </c>
       <c r="D215" s="8" t="n">
-        <v>371</v>
+        <v>435</v>
       </c>
       <c r="E215" s="9" t="n">
-        <v>38.6</v>
+        <v>38.3</v>
       </c>
     </row>
     <row r="216">
@@ -9150,10 +9174,10 @@
         </is>
       </c>
       <c r="D216" s="8" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="E216" s="9" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="217">
@@ -9196,10 +9220,10 @@
         </is>
       </c>
       <c r="D218" s="8" t="n">
-        <v>195</v>
+        <v>240</v>
       </c>
       <c r="E218" s="9" t="n">
-        <v>75.3</v>
+        <v>75.90000000000001</v>
       </c>
     </row>
     <row r="219">
@@ -9219,7 +9243,7 @@
         </is>
       </c>
       <c r="D219" s="8" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E219" s="9" t="n">
         <v>13.9</v>
@@ -9242,10 +9266,10 @@
         </is>
       </c>
       <c r="D220" s="8" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E220" s="9" t="n">
-        <v>10.8</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="221">
@@ -9265,10 +9289,10 @@
         </is>
       </c>
       <c r="D221" s="8" t="n">
-        <v>234</v>
+        <v>289</v>
       </c>
       <c r="E221" s="9" t="n">
-        <v>90.3</v>
+        <v>91.5</v>
       </c>
     </row>
     <row r="222">
@@ -9288,10 +9312,10 @@
         </is>
       </c>
       <c r="D222" s="8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E222" s="9" t="n">
-        <v>7.3</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="223">
@@ -9311,10 +9335,10 @@
         </is>
       </c>
       <c r="D223" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E223" s="9" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="224">
@@ -9337,7 +9361,7 @@
         <v>2</v>
       </c>
       <c r="E224" s="9" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="225">
@@ -9357,10 +9381,10 @@
         </is>
       </c>
       <c r="D225" s="8" t="n">
-        <v>122</v>
+        <v>154</v>
       </c>
       <c r="E225" s="9" t="n">
-        <v>47.1</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="226">
@@ -9380,10 +9404,10 @@
         </is>
       </c>
       <c r="D226" s="8" t="n">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="E226" s="9" t="n">
-        <v>29.7</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="227">
@@ -9403,10 +9427,10 @@
         </is>
       </c>
       <c r="D227" s="8" t="n">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="E227" s="9" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
     </row>
     <row r="228">
@@ -9426,10 +9450,10 @@
         </is>
       </c>
       <c r="D228" s="8" t="n">
-        <v>226</v>
+        <v>270</v>
       </c>
       <c r="E228" s="9" t="n">
-        <v>87.3</v>
+        <v>85.40000000000001</v>
       </c>
     </row>
     <row r="229">
@@ -9449,10 +9473,10 @@
         </is>
       </c>
       <c r="D229" s="8" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E229" s="9" t="n">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="230">
@@ -9472,10 +9496,10 @@
         </is>
       </c>
       <c r="D230" s="8" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E230" s="9" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="231">
@@ -9495,10 +9519,10 @@
         </is>
       </c>
       <c r="D231" s="8" t="n">
-        <v>116</v>
+        <v>143</v>
       </c>
       <c r="E231" s="9" t="n">
-        <v>44.8</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="232">
@@ -9518,10 +9542,10 @@
         </is>
       </c>
       <c r="D232" s="8" t="n">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="E232" s="9" t="n">
-        <v>44.4</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="233">
@@ -9541,10 +9565,10 @@
         </is>
       </c>
       <c r="D233" s="8" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="E233" s="9" t="n">
-        <v>10.8</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="234">
@@ -9564,10 +9588,10 @@
         </is>
       </c>
       <c r="D234" s="8" t="n">
-        <v>3570</v>
+        <v>4098</v>
       </c>
       <c r="E234" s="9" t="n">
-        <v>69.2</v>
+        <v>68.90000000000001</v>
       </c>
     </row>
     <row r="235">
@@ -9587,10 +9611,10 @@
         </is>
       </c>
       <c r="D235" s="8" t="n">
-        <v>810</v>
+        <v>938</v>
       </c>
       <c r="E235" s="9" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="236">
@@ -9610,10 +9634,10 @@
         </is>
       </c>
       <c r="D236" s="8" t="n">
-        <v>780</v>
+        <v>910</v>
       </c>
       <c r="E236" s="9" t="n">
-        <v>15.1</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="237">
@@ -9633,10 +9657,10 @@
         </is>
       </c>
       <c r="D237" s="8" t="n">
-        <v>4518</v>
+        <v>5195</v>
       </c>
       <c r="E237" s="9" t="n">
-        <v>87.59999999999999</v>
+        <v>87.40000000000001</v>
       </c>
     </row>
     <row r="238">
@@ -9656,10 +9680,10 @@
         </is>
       </c>
       <c r="D238" s="8" t="n">
-        <v>454</v>
+        <v>536</v>
       </c>
       <c r="E238" s="9" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
     </row>
     <row r="239">
@@ -9679,7 +9703,7 @@
         </is>
       </c>
       <c r="D239" s="8" t="n">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="E239" s="9" t="n">
         <v>2.1</v>
@@ -9702,7 +9726,7 @@
         </is>
       </c>
       <c r="D240" s="8" t="n">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="E240" s="9" t="n">
         <v>1.6</v>
@@ -9725,10 +9749,10 @@
         </is>
       </c>
       <c r="D241" s="8" t="n">
-        <v>2685</v>
+        <v>3083</v>
       </c>
       <c r="E241" s="9" t="n">
-        <v>52</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="242">
@@ -9748,10 +9772,10 @@
         </is>
       </c>
       <c r="D242" s="8" t="n">
-        <v>1445</v>
+        <v>1677</v>
       </c>
       <c r="E242" s="9" t="n">
-        <v>28</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="243">
@@ -9771,10 +9795,10 @@
         </is>
       </c>
       <c r="D243" s="8" t="n">
-        <v>1030</v>
+        <v>1186</v>
       </c>
       <c r="E243" s="9" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="244">
@@ -9794,10 +9818,10 @@
         </is>
       </c>
       <c r="D244" s="8" t="n">
-        <v>4470</v>
+        <v>5122</v>
       </c>
       <c r="E244" s="9" t="n">
-        <v>86.59999999999999</v>
+        <v>86.09999999999999</v>
       </c>
     </row>
     <row r="245">
@@ -9817,10 +9841,10 @@
         </is>
       </c>
       <c r="D245" s="8" t="n">
-        <v>434</v>
+        <v>508</v>
       </c>
       <c r="E245" s="9" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="246">
@@ -9840,10 +9864,10 @@
         </is>
       </c>
       <c r="D246" s="8" t="n">
-        <v>256</v>
+        <v>316</v>
       </c>
       <c r="E246" s="9" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="247">
@@ -9863,10 +9887,10 @@
         </is>
       </c>
       <c r="D247" s="8" t="n">
-        <v>2766</v>
+        <v>3155</v>
       </c>
       <c r="E247" s="9" t="n">
-        <v>53.6</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="248">
@@ -9886,10 +9910,10 @@
         </is>
       </c>
       <c r="D248" s="8" t="n">
-        <v>1925</v>
+        <v>2235</v>
       </c>
       <c r="E248" s="9" t="n">
-        <v>37.3</v>
+        <v>37.6</v>
       </c>
     </row>
     <row r="249">
@@ -9909,10 +9933,10 @@
         </is>
       </c>
       <c r="D249" s="8" t="n">
-        <v>430</v>
+        <v>517</v>
       </c>
       <c r="E249" s="9" t="n">
-        <v>8.300000000000001</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="250">
@@ -9935,7 +9959,7 @@
         <v>39</v>
       </c>
       <c r="E250" s="9" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="251">
@@ -9955,10 +9979,10 @@
         </is>
       </c>
       <c r="D251" s="8" t="n">
-        <v>196</v>
+        <v>248</v>
       </c>
       <c r="E251" s="9" t="n">
-        <v>77.8</v>
+        <v>78.7</v>
       </c>
     </row>
     <row r="252">
@@ -9978,10 +10002,10 @@
         </is>
       </c>
       <c r="D252" s="8" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E252" s="9" t="n">
-        <v>14.7</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="253">
@@ -10001,10 +10025,10 @@
         </is>
       </c>
       <c r="D253" s="8" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E253" s="9" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="254">
@@ -10024,10 +10048,10 @@
         </is>
       </c>
       <c r="D254" s="8" t="n">
-        <v>230</v>
+        <v>291</v>
       </c>
       <c r="E254" s="9" t="n">
-        <v>91.3</v>
+        <v>92.40000000000001</v>
       </c>
     </row>
     <row r="255">
@@ -10047,10 +10071,10 @@
         </is>
       </c>
       <c r="D255" s="8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E255" s="9" t="n">
-        <v>6.7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="256">
@@ -10073,7 +10097,7 @@
         <v>3</v>
       </c>
       <c r="E256" s="9" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="257">
@@ -10096,7 +10120,7 @@
         <v>2</v>
       </c>
       <c r="E257" s="9" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="258">
@@ -10116,10 +10140,10 @@
         </is>
       </c>
       <c r="D258" s="8" t="n">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="E258" s="9" t="n">
-        <v>45.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="259">
@@ -10139,10 +10163,10 @@
         </is>
       </c>
       <c r="D259" s="8" t="n">
-        <v>90</v>
+        <v>117</v>
       </c>
       <c r="E259" s="9" t="n">
-        <v>35.7</v>
+        <v>37.1</v>
       </c>
     </row>
     <row r="260">
@@ -10162,10 +10186,10 @@
         </is>
       </c>
       <c r="D260" s="8" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="E260" s="9" t="n">
-        <v>19</v>
+        <v>18.1</v>
       </c>
     </row>
     <row r="261">
@@ -10185,10 +10209,10 @@
         </is>
       </c>
       <c r="D261" s="8" t="n">
-        <v>213</v>
+        <v>270</v>
       </c>
       <c r="E261" s="9" t="n">
-        <v>84.5</v>
+        <v>85.7</v>
       </c>
     </row>
     <row r="262">
@@ -10208,10 +10232,10 @@
         </is>
       </c>
       <c r="D262" s="8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E262" s="9" t="n">
-        <v>9.1</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="263">
@@ -10231,10 +10255,10 @@
         </is>
       </c>
       <c r="D263" s="8" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E263" s="9" t="n">
-        <v>6.3</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="264">
@@ -10254,10 +10278,10 @@
         </is>
       </c>
       <c r="D264" s="8" t="n">
-        <v>135</v>
+        <v>170</v>
       </c>
       <c r="E264" s="9" t="n">
-        <v>53.6</v>
+        <v>54</v>
       </c>
     </row>
     <row r="265">
@@ -10277,10 +10301,10 @@
         </is>
       </c>
       <c r="D265" s="8" t="n">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="E265" s="9" t="n">
-        <v>36.9</v>
+        <v>36.2</v>
       </c>
     </row>
     <row r="266">
@@ -10300,10 +10324,10 @@
         </is>
       </c>
       <c r="D266" s="8" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="E266" s="9" t="n">
-        <v>9.5</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="267">
@@ -10323,10 +10347,10 @@
         </is>
       </c>
       <c r="D267" s="8" t="n">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="E267" s="9" t="n">
-        <v>72.59999999999999</v>
+        <v>73.7</v>
       </c>
     </row>
     <row r="268">
@@ -10346,10 +10370,10 @@
         </is>
       </c>
       <c r="D268" s="8" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E268" s="9" t="n">
-        <v>16.1</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="269">
@@ -10369,10 +10393,10 @@
         </is>
       </c>
       <c r="D269" s="8" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E269" s="9" t="n">
-        <v>11.3</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="270">
@@ -10392,10 +10416,10 @@
         </is>
       </c>
       <c r="D270" s="8" t="n">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="E270" s="9" t="n">
-        <v>94.59999999999999</v>
+        <v>94.2</v>
       </c>
     </row>
     <row r="271">
@@ -10415,10 +10439,10 @@
         </is>
       </c>
       <c r="D271" s="8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E271" s="9" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="272">
@@ -10441,7 +10465,7 @@
         <v>1</v>
       </c>
       <c r="E272" s="9" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="273">
@@ -10461,10 +10485,10 @@
         </is>
       </c>
       <c r="D273" s="8" t="n">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="E273" s="9" t="n">
-        <v>83.90000000000001</v>
+        <v>81.59999999999999</v>
       </c>
     </row>
     <row r="274">
@@ -10484,10 +10508,10 @@
         </is>
       </c>
       <c r="D274" s="8" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E274" s="9" t="n">
-        <v>8.9</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="275">
@@ -10507,10 +10531,10 @@
         </is>
       </c>
       <c r="D275" s="8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E275" s="9" t="n">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="276">
@@ -10530,10 +10554,10 @@
         </is>
       </c>
       <c r="D276" s="8" t="n">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="E276" s="9" t="n">
-        <v>88.7</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="277">
@@ -10553,10 +10577,10 @@
         </is>
       </c>
       <c r="D277" s="8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E277" s="9" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="278">
@@ -10579,7 +10603,7 @@
         <v>5</v>
       </c>
       <c r="E278" s="9" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="279">
@@ -10599,10 +10623,10 @@
         </is>
       </c>
       <c r="D279" s="8" t="n">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="E279" s="9" t="n">
-        <v>75</v>
+        <v>77.40000000000001</v>
       </c>
     </row>
     <row r="280">
@@ -10622,10 +10646,10 @@
         </is>
       </c>
       <c r="D280" s="8" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E280" s="9" t="n">
-        <v>20.8</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="281">
@@ -10648,7 +10672,7 @@
         <v>7</v>
       </c>
       <c r="E281" s="9" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="282">
@@ -10668,10 +10692,10 @@
         </is>
       </c>
       <c r="D282" s="8" t="n">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="E282" s="9" t="n">
-        <v>58.5</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="283">
@@ -10691,10 +10715,10 @@
         </is>
       </c>
       <c r="D283" s="8" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="E283" s="9" t="n">
-        <v>25.1</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="284">
@@ -10714,10 +10738,10 @@
         </is>
       </c>
       <c r="D284" s="8" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E284" s="9" t="n">
-        <v>16.4</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="285">
@@ -10737,10 +10761,10 @@
         </is>
       </c>
       <c r="D285" s="8" t="n">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="E285" s="9" t="n">
-        <v>74.90000000000001</v>
+        <v>74.59999999999999</v>
       </c>
     </row>
     <row r="286">
@@ -10760,10 +10784,10 @@
         </is>
       </c>
       <c r="D286" s="8" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E286" s="9" t="n">
-        <v>18.4</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="287">
@@ -10783,10 +10807,10 @@
         </is>
       </c>
       <c r="D287" s="8" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E287" s="9" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="288">
@@ -10809,7 +10833,7 @@
         <v>3</v>
       </c>
       <c r="E288" s="9" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="289">
@@ -10829,10 +10853,10 @@
         </is>
       </c>
       <c r="D289" s="8" t="n">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="E289" s="9" t="n">
-        <v>39.6</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="290">
@@ -10852,10 +10876,10 @@
         </is>
       </c>
       <c r="D290" s="8" t="n">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="E290" s="9" t="n">
-        <v>38.2</v>
+        <v>37.7</v>
       </c>
     </row>
     <row r="291">
@@ -10875,10 +10899,10 @@
         </is>
       </c>
       <c r="D291" s="8" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="E291" s="9" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="292">
@@ -10898,10 +10922,10 @@
         </is>
       </c>
       <c r="D292" s="8" t="n">
-        <v>183</v>
+        <v>203</v>
       </c>
       <c r="E292" s="9" t="n">
-        <v>88.40000000000001</v>
+        <v>89</v>
       </c>
     </row>
     <row r="293">
@@ -10921,10 +10945,10 @@
         </is>
       </c>
       <c r="D293" s="8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E293" s="9" t="n">
-        <v>10.6</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="294">
@@ -10947,7 +10971,7 @@
         <v>2</v>
       </c>
       <c r="E294" s="9" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="295">
@@ -10967,10 +10991,10 @@
         </is>
       </c>
       <c r="D295" s="8" t="n">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="E295" s="9" t="n">
-        <v>57</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="296">
@@ -10990,10 +11014,10 @@
         </is>
       </c>
       <c r="D296" s="8" t="n">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="E296" s="9" t="n">
-        <v>40.6</v>
+        <v>40.8</v>
       </c>
     </row>
     <row r="297">
@@ -11013,10 +11037,10 @@
         </is>
       </c>
       <c r="D297" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E297" s="9" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="298">
@@ -11039,7 +11063,7 @@
         <v>1</v>
       </c>
       <c r="E298" s="9" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="299">
@@ -11059,10 +11083,10 @@
         </is>
       </c>
       <c r="D299" s="8" t="n">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="E299" s="9" t="n">
-        <v>78.8</v>
+        <v>80</v>
       </c>
     </row>
     <row r="300">
@@ -11082,10 +11106,10 @@
         </is>
       </c>
       <c r="D300" s="8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E300" s="9" t="n">
-        <v>18.2</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="301">
@@ -11108,7 +11132,7 @@
         <v>4</v>
       </c>
       <c r="E301" s="9" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="302">
@@ -11128,10 +11152,10 @@
         </is>
       </c>
       <c r="D302" s="8" t="n">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="E302" s="9" t="n">
-        <v>93.40000000000001</v>
+        <v>94</v>
       </c>
     </row>
     <row r="303">
@@ -11154,7 +11178,7 @@
         <v>8</v>
       </c>
       <c r="E303" s="9" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="304">
@@ -11197,10 +11221,10 @@
         </is>
       </c>
       <c r="D305" s="8" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E305" s="9" t="n">
-        <v>47.4</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="306">
@@ -11220,10 +11244,10 @@
         </is>
       </c>
       <c r="D306" s="8" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E306" s="9" t="n">
-        <v>36.5</v>
+        <v>37.3</v>
       </c>
     </row>
     <row r="307">
@@ -11243,10 +11267,10 @@
         </is>
       </c>
       <c r="D307" s="8" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E307" s="9" t="n">
-        <v>16.1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="308">
@@ -11266,10 +11290,10 @@
         </is>
       </c>
       <c r="D308" s="8" t="n">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="E308" s="9" t="n">
-        <v>86.09999999999999</v>
+        <v>86.7</v>
       </c>
     </row>
     <row r="309">
@@ -11289,10 +11313,10 @@
         </is>
       </c>
       <c r="D309" s="8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E309" s="9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="310">
@@ -11315,7 +11339,7 @@
         <v>7</v>
       </c>
       <c r="E310" s="9" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="311">
@@ -11335,10 +11359,10 @@
         </is>
       </c>
       <c r="D311" s="8" t="n">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="E311" s="9" t="n">
-        <v>73</v>
+        <v>72.7</v>
       </c>
     </row>
     <row r="312">
@@ -11358,10 +11382,10 @@
         </is>
       </c>
       <c r="D312" s="8" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E312" s="9" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="313">
@@ -11381,10 +11405,10 @@
         </is>
       </c>
       <c r="D313" s="8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E313" s="9" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="314">
@@ -11407,7 +11431,7 @@
         <v>5</v>
       </c>
       <c r="E314" s="9" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="315">
@@ -11427,10 +11451,10 @@
         </is>
       </c>
       <c r="D315" s="8" t="n">
-        <v>405</v>
+        <v>461</v>
       </c>
       <c r="E315" s="9" t="n">
-        <v>71.90000000000001</v>
+        <v>73.2</v>
       </c>
     </row>
     <row r="316">
@@ -11450,10 +11474,10 @@
         </is>
       </c>
       <c r="D316" s="8" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E316" s="9" t="n">
-        <v>19</v>
+        <v>17.9</v>
       </c>
     </row>
     <row r="317">
@@ -11473,10 +11497,10 @@
         </is>
       </c>
       <c r="D317" s="8" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E317" s="9" t="n">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="318">
@@ -11496,10 +11520,10 @@
         </is>
       </c>
       <c r="D318" s="8" t="n">
-        <v>512</v>
+        <v>576</v>
       </c>
       <c r="E318" s="9" t="n">
-        <v>90.90000000000001</v>
+        <v>91.40000000000001</v>
       </c>
     </row>
     <row r="319">
@@ -11519,10 +11543,10 @@
         </is>
       </c>
       <c r="D319" s="8" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E319" s="9" t="n">
-        <v>7.8</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="320">
@@ -11538,14 +11562,14 @@
       </c>
       <c r="C320" s="7" t="inlineStr">
         <is>
-          <t>Divorciado/a</t>
+          <t>Viudo/a</t>
         </is>
       </c>
       <c r="D320" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E320" s="9" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="321">
@@ -11561,14 +11585,14 @@
       </c>
       <c r="C321" s="7" t="inlineStr">
         <is>
-          <t>Viudo/a</t>
+          <t>Divorciado/a</t>
         </is>
       </c>
       <c r="D321" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E321" s="9" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="322">
@@ -11588,10 +11612,10 @@
         </is>
       </c>
       <c r="D322" s="8" t="n">
-        <v>296</v>
+        <v>327</v>
       </c>
       <c r="E322" s="9" t="n">
-        <v>52.6</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="323">
@@ -11611,10 +11635,10 @@
         </is>
       </c>
       <c r="D323" s="8" t="n">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="E323" s="9" t="n">
-        <v>25</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="324">
@@ -11634,10 +11658,10 @@
         </is>
       </c>
       <c r="D324" s="8" t="n">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="E324" s="9" t="n">
-        <v>22.4</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="325">
@@ -11657,10 +11681,10 @@
         </is>
       </c>
       <c r="D325" s="8" t="n">
-        <v>468</v>
+        <v>527</v>
       </c>
       <c r="E325" s="9" t="n">
-        <v>83.09999999999999</v>
+        <v>83.7</v>
       </c>
     </row>
     <row r="326">
@@ -11680,10 +11704,10 @@
         </is>
       </c>
       <c r="D326" s="8" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E326" s="9" t="n">
-        <v>11.7</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="327">
@@ -11703,7 +11727,7 @@
         </is>
       </c>
       <c r="D327" s="8" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E327" s="9" t="n">
         <v>5.2</v>
@@ -11726,10 +11750,10 @@
         </is>
       </c>
       <c r="D328" s="8" t="n">
-        <v>286</v>
+        <v>311</v>
       </c>
       <c r="E328" s="9" t="n">
-        <v>50.8</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="329">
@@ -11749,10 +11773,10 @@
         </is>
       </c>
       <c r="D329" s="8" t="n">
-        <v>227</v>
+        <v>265</v>
       </c>
       <c r="E329" s="9" t="n">
-        <v>40.3</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="330">
@@ -11772,10 +11796,10 @@
         </is>
       </c>
       <c r="D330" s="8" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E330" s="9" t="n">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="331">
@@ -11795,10 +11819,10 @@
         </is>
       </c>
       <c r="D331" s="8" t="n">
-        <v>276</v>
+        <v>316</v>
       </c>
       <c r="E331" s="9" t="n">
-        <v>60.7</v>
+        <v>62.1</v>
       </c>
     </row>
     <row r="332">
@@ -11818,10 +11842,10 @@
         </is>
       </c>
       <c r="D332" s="8" t="n">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="E332" s="9" t="n">
-        <v>22.9</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="333">
@@ -11841,10 +11865,10 @@
         </is>
       </c>
       <c r="D333" s="8" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="E333" s="9" t="n">
-        <v>16.5</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="334">
@@ -11864,7 +11888,7 @@
         </is>
       </c>
       <c r="D334" s="8" t="n">
-        <v>380</v>
+        <v>425</v>
       </c>
       <c r="E334" s="9" t="n">
         <v>83.5</v>
@@ -11887,10 +11911,10 @@
         </is>
       </c>
       <c r="D335" s="8" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="E335" s="9" t="n">
-        <v>11.9</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="336">
@@ -11910,10 +11934,10 @@
         </is>
       </c>
       <c r="D336" s="8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E336" s="9" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="337">
@@ -11936,7 +11960,7 @@
         <v>3</v>
       </c>
       <c r="E337" s="9" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="338">
@@ -11956,10 +11980,10 @@
         </is>
       </c>
       <c r="D338" s="8" t="n">
-        <v>221</v>
+        <v>246</v>
       </c>
       <c r="E338" s="9" t="n">
-        <v>48.6</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="339">
@@ -11979,10 +12003,10 @@
         </is>
       </c>
       <c r="D339" s="8" t="n">
-        <v>176</v>
+        <v>201</v>
       </c>
       <c r="E339" s="9" t="n">
-        <v>38.7</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="340">
@@ -12002,10 +12026,10 @@
         </is>
       </c>
       <c r="D340" s="8" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E340" s="9" t="n">
-        <v>12.7</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="341">
@@ -12025,10 +12049,10 @@
         </is>
       </c>
       <c r="D341" s="8" t="n">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="E341" s="9" t="n">
-        <v>87.90000000000001</v>
+        <v>88.40000000000001</v>
       </c>
     </row>
     <row r="342">
@@ -12048,10 +12072,10 @@
         </is>
       </c>
       <c r="D342" s="8" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E342" s="9" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="343">
@@ -12071,10 +12095,10 @@
         </is>
       </c>
       <c r="D343" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E343" s="9" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="344">
@@ -12094,10 +12118,10 @@
         </is>
       </c>
       <c r="D344" s="8" t="n">
-        <v>237</v>
+        <v>270</v>
       </c>
       <c r="E344" s="9" t="n">
-        <v>52.1</v>
+        <v>53</v>
       </c>
     </row>
     <row r="345">
@@ -12117,10 +12141,10 @@
         </is>
       </c>
       <c r="D345" s="8" t="n">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="E345" s="9" t="n">
-        <v>43.7</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="346">
@@ -12140,10 +12164,10 @@
         </is>
       </c>
       <c r="D346" s="8" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E346" s="9" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="347">
@@ -12186,10 +12210,10 @@
         </is>
       </c>
       <c r="D348" s="8" t="n">
-        <v>380</v>
+        <v>454</v>
       </c>
       <c r="E348" s="9" t="n">
-        <v>61.8</v>
+        <v>63.5</v>
       </c>
     </row>
     <row r="349">
@@ -12209,10 +12233,10 @@
         </is>
       </c>
       <c r="D349" s="8" t="n">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="E349" s="9" t="n">
-        <v>29.1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="350">
@@ -12232,10 +12256,10 @@
         </is>
       </c>
       <c r="D350" s="8" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E350" s="9" t="n">
-        <v>9.1</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="351">
@@ -12255,10 +12279,10 @@
         </is>
       </c>
       <c r="D351" s="8" t="n">
-        <v>554</v>
+        <v>646</v>
       </c>
       <c r="E351" s="9" t="n">
-        <v>90.09999999999999</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="352">
@@ -12278,10 +12302,10 @@
         </is>
       </c>
       <c r="D352" s="8" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E352" s="9" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="353">
@@ -12301,10 +12325,10 @@
         </is>
       </c>
       <c r="D353" s="8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E353" s="9" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="354">
@@ -12324,10 +12348,10 @@
         </is>
       </c>
       <c r="D354" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E354" s="9" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="355">
@@ -12347,10 +12371,10 @@
         </is>
       </c>
       <c r="D355" s="8" t="n">
-        <v>330</v>
+        <v>372</v>
       </c>
       <c r="E355" s="9" t="n">
-        <v>53.7</v>
+        <v>52</v>
       </c>
     </row>
     <row r="356">
@@ -12370,10 +12394,10 @@
         </is>
       </c>
       <c r="D356" s="8" t="n">
-        <v>175</v>
+        <v>211</v>
       </c>
       <c r="E356" s="9" t="n">
-        <v>28.5</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="357">
@@ -12393,10 +12417,10 @@
         </is>
       </c>
       <c r="D357" s="8" t="n">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="E357" s="9" t="n">
-        <v>17.9</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="358">
@@ -12416,10 +12440,10 @@
         </is>
       </c>
       <c r="D358" s="8" t="n">
-        <v>468</v>
+        <v>551</v>
       </c>
       <c r="E358" s="9" t="n">
-        <v>76.09999999999999</v>
+        <v>77.09999999999999</v>
       </c>
     </row>
     <row r="359">
@@ -12439,10 +12463,10 @@
         </is>
       </c>
       <c r="D359" s="8" t="n">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="E359" s="9" t="n">
-        <v>18.5</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="360">
@@ -12462,10 +12486,10 @@
         </is>
       </c>
       <c r="D360" s="8" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="E360" s="9" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="361">
@@ -12485,10 +12509,10 @@
         </is>
       </c>
       <c r="D361" s="8" t="n">
-        <v>340</v>
+        <v>393</v>
       </c>
       <c r="E361" s="9" t="n">
-        <v>55.3</v>
+        <v>55</v>
       </c>
     </row>
     <row r="362">
@@ -12508,10 +12532,10 @@
         </is>
       </c>
       <c r="D362" s="8" t="n">
-        <v>214</v>
+        <v>245</v>
       </c>
       <c r="E362" s="9" t="n">
-        <v>34.8</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="363">
@@ -12531,10 +12555,10 @@
         </is>
       </c>
       <c r="D363" s="8" t="n">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="E363" s="9" t="n">
-        <v>9.6</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="364">
@@ -12554,10 +12578,10 @@
         </is>
       </c>
       <c r="D364" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E364" s="9" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="365">
@@ -12577,10 +12601,10 @@
         </is>
       </c>
       <c r="D365" s="8" t="n">
-        <v>216</v>
+        <v>239</v>
       </c>
       <c r="E365" s="9" t="n">
-        <v>72.5</v>
+        <v>72.2</v>
       </c>
     </row>
     <row r="366">
@@ -12600,10 +12624,10 @@
         </is>
       </c>
       <c r="D366" s="8" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E366" s="9" t="n">
-        <v>18.1</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="367">
@@ -12623,10 +12647,10 @@
         </is>
       </c>
       <c r="D367" s="8" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E367" s="9" t="n">
-        <v>9.4</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="368">
@@ -12646,10 +12670,10 @@
         </is>
       </c>
       <c r="D368" s="8" t="n">
-        <v>263</v>
+        <v>292</v>
       </c>
       <c r="E368" s="9" t="n">
-        <v>88.3</v>
+        <v>88.2</v>
       </c>
     </row>
     <row r="369">
@@ -12669,10 +12693,10 @@
         </is>
       </c>
       <c r="D369" s="8" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E369" s="9" t="n">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="370">
@@ -12692,10 +12716,10 @@
         </is>
       </c>
       <c r="D370" s="8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E370" s="9" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="371">
@@ -12715,10 +12739,10 @@
         </is>
       </c>
       <c r="D371" s="8" t="n">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="E371" s="9" t="n">
-        <v>56.7</v>
+        <v>56.5</v>
       </c>
     </row>
     <row r="372">
@@ -12738,10 +12762,10 @@
         </is>
       </c>
       <c r="D372" s="8" t="n">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="E372" s="9" t="n">
-        <v>25.5</v>
+        <v>25.1</v>
       </c>
     </row>
     <row r="373">
@@ -12761,10 +12785,10 @@
         </is>
       </c>
       <c r="D373" s="8" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E373" s="9" t="n">
-        <v>17.8</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="374">
@@ -12784,10 +12808,10 @@
         </is>
       </c>
       <c r="D374" s="8" t="n">
-        <v>255</v>
+        <v>284</v>
       </c>
       <c r="E374" s="9" t="n">
-        <v>85.59999999999999</v>
+        <v>85.8</v>
       </c>
     </row>
     <row r="375">
@@ -12807,10 +12831,10 @@
         </is>
       </c>
       <c r="D375" s="8" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E375" s="9" t="n">
-        <v>11.1</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="376">
@@ -12830,10 +12854,10 @@
         </is>
       </c>
       <c r="D376" s="8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E376" s="9" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="377">
@@ -12853,10 +12877,10 @@
         </is>
       </c>
       <c r="D377" s="8" t="n">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="E377" s="9" t="n">
-        <v>61.1</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="378">
@@ -12876,10 +12900,10 @@
         </is>
       </c>
       <c r="D378" s="8" t="n">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="E378" s="9" t="n">
-        <v>31.5</v>
+        <v>31.4</v>
       </c>
     </row>
     <row r="379">
@@ -12899,10 +12923,10 @@
         </is>
       </c>
       <c r="D379" s="8" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E379" s="9" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="380">
@@ -12945,10 +12969,10 @@
         </is>
       </c>
       <c r="D381" s="8" t="n">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="E381" s="9" t="n">
-        <v>75.7</v>
+        <v>76.5</v>
       </c>
     </row>
     <row r="382">
@@ -12968,10 +12992,10 @@
         </is>
       </c>
       <c r="D382" s="8" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E382" s="9" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="383">
@@ -12991,10 +13015,10 @@
         </is>
       </c>
       <c r="D383" s="8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E383" s="9" t="n">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="384">
@@ -13014,10 +13038,10 @@
         </is>
       </c>
       <c r="D384" s="8" t="n">
-        <v>162</v>
+        <v>188</v>
       </c>
       <c r="E384" s="9" t="n">
-        <v>93.59999999999999</v>
+        <v>94</v>
       </c>
     </row>
     <row r="385">
@@ -13037,7 +13061,7 @@
         </is>
       </c>
       <c r="D385" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E385" s="9" t="n">
         <v>3.5</v>
@@ -13063,7 +13087,7 @@
         <v>5</v>
       </c>
       <c r="E386" s="9" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="387">
@@ -13083,10 +13107,10 @@
         </is>
       </c>
       <c r="D387" s="8" t="n">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="E387" s="9" t="n">
-        <v>51.4</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="388">
@@ -13106,10 +13130,10 @@
         </is>
       </c>
       <c r="D388" s="8" t="n">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="E388" s="9" t="n">
-        <v>35.3</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="389">
@@ -13129,10 +13153,10 @@
         </is>
       </c>
       <c r="D389" s="8" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E389" s="9" t="n">
-        <v>13.3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="390">
@@ -13152,10 +13176,10 @@
         </is>
       </c>
       <c r="D390" s="8" t="n">
-        <v>144</v>
+        <v>169</v>
       </c>
       <c r="E390" s="9" t="n">
-        <v>83.2</v>
+        <v>84.5</v>
       </c>
     </row>
     <row r="391">
@@ -13175,10 +13199,10 @@
         </is>
       </c>
       <c r="D391" s="8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E391" s="9" t="n">
-        <v>13.3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="392">
@@ -13198,7 +13222,7 @@
         </is>
       </c>
       <c r="D392" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E392" s="9" t="n">
         <v>3.5</v>
@@ -13221,10 +13245,10 @@
         </is>
       </c>
       <c r="D393" s="8" t="n">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="E393" s="9" t="n">
-        <v>57.8</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="394">
@@ -13244,10 +13268,10 @@
         </is>
       </c>
       <c r="D394" s="8" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="E394" s="9" t="n">
-        <v>37.6</v>
+        <v>37</v>
       </c>
     </row>
     <row r="395">
@@ -13267,7 +13291,7 @@
         </is>
       </c>
       <c r="D395" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E395" s="9" t="n">
         <v>3.5</v>
@@ -13293,7 +13317,7 @@
         <v>2</v>
       </c>
       <c r="E396" s="9" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="397">
@@ -13313,10 +13337,10 @@
         </is>
       </c>
       <c r="D397" s="8" t="n">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="E397" s="9" t="n">
-        <v>72.3</v>
+        <v>71.8</v>
       </c>
     </row>
     <row r="398">
@@ -13336,10 +13360,10 @@
         </is>
       </c>
       <c r="D398" s="8" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="E398" s="9" t="n">
-        <v>19.9</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="399">
@@ -13359,10 +13383,10 @@
         </is>
       </c>
       <c r="D399" s="8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E399" s="9" t="n">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="400">
@@ -13382,10 +13406,10 @@
         </is>
       </c>
       <c r="D400" s="8" t="n">
-        <v>199</v>
+        <v>225</v>
       </c>
       <c r="E400" s="9" t="n">
-        <v>96.59999999999999</v>
+        <v>96.2</v>
       </c>
     </row>
     <row r="401">
@@ -13405,10 +13429,10 @@
         </is>
       </c>
       <c r="D401" s="8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E401" s="9" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="402">
@@ -13428,10 +13452,10 @@
         </is>
       </c>
       <c r="D402" s="8" t="n">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="E402" s="9" t="n">
-        <v>48.1</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="403">
@@ -13451,10 +13475,10 @@
         </is>
       </c>
       <c r="D403" s="8" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="E403" s="9" t="n">
-        <v>35</v>
+        <v>34.6</v>
       </c>
     </row>
     <row r="404">
@@ -13474,10 +13498,10 @@
         </is>
       </c>
       <c r="D404" s="8" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E404" s="9" t="n">
-        <v>17</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="405">
@@ -13497,10 +13521,10 @@
         </is>
       </c>
       <c r="D405" s="8" t="n">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="E405" s="9" t="n">
-        <v>76.7</v>
+        <v>73.90000000000001</v>
       </c>
     </row>
     <row r="406">
@@ -13520,10 +13544,10 @@
         </is>
       </c>
       <c r="D406" s="8" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E406" s="9" t="n">
-        <v>14.1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="407">
@@ -13543,10 +13567,10 @@
         </is>
       </c>
       <c r="D407" s="8" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E407" s="9" t="n">
-        <v>9.199999999999999</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="408">
@@ -13566,10 +13590,10 @@
         </is>
       </c>
       <c r="D408" s="8" t="n">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="E408" s="9" t="n">
-        <v>41.7</v>
+        <v>41</v>
       </c>
     </row>
     <row r="409">
@@ -13589,10 +13613,10 @@
         </is>
       </c>
       <c r="D409" s="8" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="E409" s="9" t="n">
-        <v>38.3</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="410">
@@ -13612,10 +13636,10 @@
         </is>
       </c>
       <c r="D410" s="8" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E410" s="9" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="411">
@@ -13638,7 +13662,7 @@
         <v>7</v>
       </c>
       <c r="E411" s="9" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
